--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,22 +418,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -458,10 +446,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2437</v>
+        <v>2455</v>
       </c>
       <c r="C2" t="n">
-        <v>2435</v>
+        <v>2453</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
@@ -474,13 +462,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1924</v>
+        <v>1929</v>
       </c>
       <c r="C3" t="n">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="D3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>608</v>
+        <v>762</v>
       </c>
       <c r="C4" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D4" t="n">
-        <v>336</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +494,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56</v>
+        <v>258</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6">
@@ -546,27 +534,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -580,10 +568,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2437</v>
+        <v>2455</v>
       </c>
       <c r="D2" t="n">
-        <v>2435</v>
+        <v>2453</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -649,115 +637,115 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Asma Bibi</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373641</v>
+        <v>373692</v>
       </c>
       <c r="C6" t="n">
-        <v>134</v>
+        <v>285</v>
       </c>
       <c r="D6" t="n">
         <v>112</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Asma Bibi</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373642</v>
+        <v>373641</v>
       </c>
       <c r="C7" t="n">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="D7" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373684</v>
+        <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="D8" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373649</v>
+        <v>373684</v>
       </c>
       <c r="C9" t="n">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="D9" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373692</v>
+        <v>373658</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373658</v>
+        <v>373649</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E11" t="n">
-        <v>81</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -770,162 +758,162 @@
         <v>373691</v>
       </c>
       <c r="C12" t="n">
-        <v>174</v>
+        <v>271</v>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Furqan Ullah Khan</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373683</v>
+        <v>373712</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>244</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Furqan Ullah Khan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373673</v>
+        <v>373683</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Muhammad Yousaf</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373690</v>
+        <v>373673</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Muhammad Yousaf</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373651</v>
+        <v>373690</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373716</v>
+        <v>373651</v>
       </c>
       <c r="C17" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jaweria</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>163495</v>
+        <v>373716</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Jaweria</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>373671</v>
+        <v>163495</v>
       </c>
       <c r="C19" t="n">
+        <v>56</v>
+      </c>
+      <c r="D19" t="n">
         <v>55</v>
       </c>
-      <c r="D19" t="n">
-        <v>51</v>
-      </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373705</v>
+        <v>373671</v>
       </c>
       <c r="C20" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E20" t="n">
         <v>4</v>
@@ -934,17 +922,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Asma Gull</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373672</v>
+        <v>373705</v>
       </c>
       <c r="C21" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D21" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
@@ -953,39 +941,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Asma Gull</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>453925</v>
+        <v>373672</v>
       </c>
       <c r="C22" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D22" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>373712</v>
+        <v>453925</v>
       </c>
       <c r="C23" t="n">
-        <v>155</v>
+        <v>44</v>
       </c>
       <c r="D23" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E23" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -998,10 +986,10 @@
         <v>564273</v>
       </c>
       <c r="C24" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>762</v>
+        <v>877</v>
       </c>
       <c r="C4" t="n">
-        <v>258</v>
+        <v>360</v>
       </c>
       <c r="D4" t="n">
-        <v>484</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5">
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>258</v>
+        <v>442</v>
       </c>
       <c r="C5" t="n">
-        <v>87</v>
+        <v>305</v>
       </c>
       <c r="D5" t="n">
         <v>137</v>
@@ -580,210 +580,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>373646</v>
+        <v>373692</v>
       </c>
       <c r="C3" t="n">
-        <v>149</v>
+        <v>334</v>
       </c>
       <c r="D3" t="n">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373696</v>
+        <v>373658</v>
       </c>
       <c r="C4" t="n">
-        <v>139</v>
+        <v>336</v>
       </c>
       <c r="D4" t="n">
-        <v>122</v>
+        <v>173</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373648</v>
+        <v>373691</v>
       </c>
       <c r="C5" t="n">
-        <v>140</v>
+        <v>339</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373692</v>
+        <v>373712</v>
       </c>
       <c r="C6" t="n">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="D6" t="n">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="E6" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Asma Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373641</v>
+        <v>373646</v>
       </c>
       <c r="C7" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="D7" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373642</v>
+        <v>373696</v>
       </c>
       <c r="C8" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="D8" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373684</v>
+        <v>373648</v>
       </c>
       <c r="C9" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D9" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Asma Bibi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373658</v>
+        <v>373641</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="D10" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E10" t="n">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373649</v>
+        <v>373642</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373691</v>
+        <v>373684</v>
       </c>
       <c r="C12" t="n">
-        <v>271</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E12" t="n">
-        <v>177</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373712</v>
+        <v>373649</v>
       </c>
       <c r="C13" t="n">
-        <v>244</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="E13" t="n">
-        <v>160</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,22 +430,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -446,10 +458,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2455</v>
+        <v>2459</v>
       </c>
       <c r="C2" t="n">
-        <v>2453</v>
+        <v>2457</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
@@ -462,10 +474,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1929</v>
+        <v>1932</v>
       </c>
       <c r="C3" t="n">
-        <v>1677</v>
+        <v>1680</v>
       </c>
       <c r="D3" t="n">
         <v>252</v>
@@ -474,33 +486,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Girls</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>877</v>
+        <v>442</v>
       </c>
       <c r="C4" t="n">
-        <v>360</v>
+        <v>222</v>
       </c>
       <c r="D4" t="n">
-        <v>508</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Girls</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>442</v>
+        <v>689</v>
       </c>
       <c r="C5" t="n">
-        <v>305</v>
+        <v>127</v>
       </c>
       <c r="D5" t="n">
-        <v>137</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6">
@@ -534,27 +546,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -568,10 +580,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2455</v>
+        <v>2459</v>
       </c>
       <c r="D2" t="n">
-        <v>2453</v>
+        <v>2457</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -580,210 +592,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>373692</v>
+        <v>373646</v>
       </c>
       <c r="C3" t="n">
-        <v>334</v>
+        <v>149</v>
       </c>
       <c r="D3" t="n">
-        <v>177</v>
+        <v>133</v>
       </c>
       <c r="E3" t="n">
-        <v>153</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373658</v>
+        <v>373696</v>
       </c>
       <c r="C4" t="n">
-        <v>336</v>
+        <v>139</v>
       </c>
       <c r="D4" t="n">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="E4" t="n">
-        <v>161</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373691</v>
+        <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>339</v>
+        <v>140</v>
       </c>
       <c r="D5" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Asma Bibi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373712</v>
+        <v>373641</v>
       </c>
       <c r="C6" t="n">
-        <v>331</v>
+        <v>134</v>
       </c>
       <c r="D6" t="n">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="E6" t="n">
-        <v>171</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373646</v>
+        <v>373684</v>
       </c>
       <c r="C7" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D7" t="n">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373696</v>
+        <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="D8" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373648</v>
+        <v>373712</v>
       </c>
       <c r="C9" t="n">
-        <v>140</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Asma Bibi</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373641</v>
+        <v>373692</v>
       </c>
       <c r="C10" t="n">
-        <v>134</v>
+        <v>288</v>
       </c>
       <c r="D10" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373642</v>
+        <v>373649</v>
       </c>
       <c r="C11" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373684</v>
+        <v>373691</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>287</v>
       </c>
       <c r="D12" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="E12" t="n">
-        <v>28</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373649</v>
+        <v>373658</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>274</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -458,10 +458,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2459</v>
+        <v>2443</v>
       </c>
       <c r="C2" t="n">
-        <v>2457</v>
+        <v>2441</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="C4" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D4" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>689</v>
+        <v>715</v>
       </c>
       <c r="C5" t="n">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="D5" t="n">
-        <v>553</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2459</v>
+        <v>2443</v>
       </c>
       <c r="D2" t="n">
-        <v>2457</v>
+        <v>2441</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -611,77 +611,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Asma Bibi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373696</v>
+        <v>373641</v>
       </c>
       <c r="C4" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="D4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373648</v>
+        <v>373696</v>
       </c>
       <c r="C5" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Asma Bibi</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373641</v>
+        <v>373648</v>
       </c>
       <c r="C6" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D6" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373684</v>
+        <v>373712</v>
       </c>
       <c r="C7" t="n">
-        <v>134</v>
+        <v>307</v>
       </c>
       <c r="D7" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8">
@@ -694,51 +694,51 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D8" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373712</v>
+        <v>373692</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E9" t="n">
-        <v>199</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373692</v>
+        <v>373684</v>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>134</v>
       </c>
       <c r="D10" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E10" t="n">
-        <v>183</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -773,7 +773,7 @@
         <v>287</v>
       </c>
       <c r="D12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E12" t="n">
         <v>201</v>
@@ -789,10 +789,10 @@
         <v>373658</v>
       </c>
       <c r="C13" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E13" t="n">
         <v>196</v>
@@ -915,36 +915,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373671</v>
+        <v>373705</v>
       </c>
       <c r="C20" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D20" t="n">
         <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373705</v>
+        <v>373671</v>
       </c>
       <c r="C21" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D21" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,22 +418,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -458,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2443</v>
+        <v>2439</v>
       </c>
       <c r="C2" t="n">
-        <v>2441</v>
+        <v>2436</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -490,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C4" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D4" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +494,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>715</v>
+        <v>729</v>
       </c>
       <c r="C5" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D5" t="n">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6">
@@ -546,27 +534,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -580,13 +568,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2443</v>
+        <v>2439</v>
       </c>
       <c r="D2" t="n">
-        <v>2441</v>
+        <v>2436</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -618,13 +606,13 @@
         <v>373641</v>
       </c>
       <c r="C4" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D4" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -675,10 +663,10 @@
         <v>373712</v>
       </c>
       <c r="C7" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D7" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E7" t="n">
         <v>199</v>
@@ -953,39 +941,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Asma Gull</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>373672</v>
+        <v>453925</v>
       </c>
       <c r="C22" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D22" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Asma Gull</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>453925</v>
+        <v>373672</v>
       </c>
       <c r="C23" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D23" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,22 +430,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -534,27 +546,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C4" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D4" t="n">
         <v>227</v>
@@ -706,39 +706,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373692</v>
+        <v>373684</v>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>134</v>
       </c>
       <c r="D9" t="n">
         <v>106</v>
       </c>
       <c r="E9" t="n">
-        <v>183</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373684</v>
+        <v>373692</v>
       </c>
       <c r="C10" t="n">
-        <v>134</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -960,10 +960,10 @@
         <v>453925</v>
       </c>
       <c r="C22" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D22" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -493,10 +493,10 @@
         <v>460</v>
       </c>
       <c r="C4" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D4" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5">
@@ -678,10 +678,10 @@
         <v>309</v>
       </c>
       <c r="D7" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E7" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,22 +418,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -546,27 +534,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -446,10 +446,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2439</v>
+        <v>2386</v>
       </c>
       <c r="C2" t="n">
-        <v>2436</v>
+        <v>2383</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="C4" t="n">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D4" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>729</v>
+        <v>797</v>
       </c>
       <c r="C5" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="D5" t="n">
-        <v>570</v>
+        <v>618</v>
       </c>
     </row>
     <row r="6">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,10 +568,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2439</v>
+        <v>2386</v>
       </c>
       <c r="D2" t="n">
-        <v>2436</v>
+        <v>2383</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -580,39 +580,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Asma Bibi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>373646</v>
+        <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="D3" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Asma Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373641</v>
+        <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D4" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E4" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -644,51 +644,51 @@
         <v>373648</v>
       </c>
       <c r="C6" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D6" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373712</v>
+        <v>373642</v>
       </c>
       <c r="C7" t="n">
-        <v>309</v>
+        <v>129</v>
       </c>
       <c r="D7" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E7" t="n">
-        <v>201</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373642</v>
+        <v>373712</v>
       </c>
       <c r="C8" t="n">
-        <v>115</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
         <v>108</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">
@@ -808,115 +808,115 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373673</v>
+        <v>373716</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Muhammad Yousaf</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373690</v>
+        <v>373673</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Muhammad Yousaf</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373651</v>
+        <v>373690</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>373716</v>
+        <v>373651</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jaweria</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>163495</v>
+        <v>373705</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Jaweria</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373705</v>
+        <v>163495</v>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -998,39 +998,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>373665</v>
+        <v>373706</v>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D25" t="n">
         <v>37</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>373706</v>
+        <v>373665</v>
       </c>
       <c r="C26" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D26" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1340,49 +1340,49 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Muhammad naeem</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>571571</v>
+        <v>373669</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Aisha Aman</t>
+          <t>Muhammad naeem</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>373704</v>
+        <v>571571</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mahnoorr</t>
+          <t>Aisha Aman</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>373670</v>
+        <v>373704</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1397,11 +1397,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Muhammad Noor</t>
+          <t>Mahnoorr</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>373701</v>
+        <v>373670</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1416,11 +1416,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Rahila Naaz</t>
+          <t>Muhammad Noor</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>373715</v>
+        <v>373701</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1435,11 +1435,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Robina Shaheen</t>
+          <t>Rahila Naaz</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>373639</v>
+        <v>373715</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -1448,6 +1448,25 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Robina Shaheen</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>373639</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2386</v>
+        <v>2352</v>
       </c>
       <c r="C2" t="n">
-        <v>2383</v>
+        <v>2345</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>479</v>
+        <v>514</v>
       </c>
       <c r="C4" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D4" t="n">
-        <v>235</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>797</v>
+        <v>907</v>
       </c>
       <c r="C5" t="n">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D5" t="n">
-        <v>618</v>
+        <v>705</v>
       </c>
     </row>
     <row r="6">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
         <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -568,13 +568,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2386</v>
+        <v>2352</v>
       </c>
       <c r="D2" t="n">
-        <v>2383</v>
+        <v>2345</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -587,13 +587,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D3" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -606,51 +606,51 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D4" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373696</v>
+        <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373648</v>
+        <v>373696</v>
       </c>
       <c r="C6" t="n">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="D6" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -663,13 +663,13 @@
         <v>373642</v>
       </c>
       <c r="C7" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D7" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -682,13 +682,13 @@
         <v>373712</v>
       </c>
       <c r="C8" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
         <v>108</v>
       </c>
       <c r="E8" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9">
@@ -789,96 +789,96 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Furqan Ullah Khan</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373683</v>
+        <v>373651</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Furqan Ullah Khan</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373716</v>
+        <v>373683</v>
       </c>
       <c r="C15" t="n">
+        <v>76</v>
+      </c>
+      <c r="D15" t="n">
         <v>68</v>
       </c>
-      <c r="D15" t="n">
-        <v>65</v>
-      </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373673</v>
+        <v>373716</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Muhammad Yousaf</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373690</v>
+        <v>373673</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Muhammad Yousaf</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>373651</v>
+        <v>373690</v>
       </c>
       <c r="C18" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -891,13 +891,13 @@
         <v>373705</v>
       </c>
       <c r="C19" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D19" t="n">
         <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -1005,13 +1005,13 @@
         <v>373706</v>
       </c>
       <c r="C25" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E25" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -1081,13 +1081,13 @@
         <v>373710</v>
       </c>
       <c r="C29" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D29" t="n">
         <v>27</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -1245,49 +1245,49 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Laiba Khan</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>373653</v>
+        <v>373669</v>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D38" t="n">
         <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Shehla Noor</t>
+          <t>Laiba Khan</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>373650</v>
+        <v>373653</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Zain Ul Abideen</t>
+          <t>Shehla Noor</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>373667</v>
+        <v>373650</v>
       </c>
       <c r="C40" t="n">
         <v>3</v>
@@ -1302,17 +1302,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Muhammad Shahid Khan</t>
+          <t>Zain Ul Abideen</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>373662</v>
+        <v>373667</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1321,39 +1321,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Chashm Gul</t>
+          <t>Muhammad Shahid Khan</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>373695</v>
+        <v>373662</v>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
         <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Chashm Gul</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>373669</v>
+        <v>373695</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2352</v>
+        <v>2238</v>
       </c>
       <c r="C2" t="n">
-        <v>2345</v>
+        <v>2229</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>514</v>
+        <v>589</v>
       </c>
       <c r="C4" t="n">
-        <v>256</v>
+        <v>308</v>
       </c>
       <c r="D4" t="n">
-        <v>258</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>907</v>
+        <v>1056</v>
       </c>
       <c r="C5" t="n">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="D5" t="n">
-        <v>705</v>
+        <v>802</v>
       </c>
     </row>
     <row r="6">
@@ -510,13 +510,29 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Girls vs Household</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -568,13 +584,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2352</v>
+        <v>2238</v>
       </c>
       <c r="D2" t="n">
-        <v>2345</v>
+        <v>2229</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -587,89 +603,89 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="D3" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373646</v>
+        <v>373648</v>
       </c>
       <c r="C4" t="n">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="D4" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373648</v>
+        <v>373646</v>
       </c>
       <c r="C5" t="n">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D5" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373696</v>
+        <v>373642</v>
       </c>
       <c r="C6" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="D6" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373642</v>
+        <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="D7" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -770,134 +786,134 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373658</v>
+        <v>373651</v>
       </c>
       <c r="C13" t="n">
-        <v>275</v>
+        <v>165</v>
       </c>
       <c r="D13" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E13" t="n">
-        <v>196</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373651</v>
+        <v>373658</v>
       </c>
       <c r="C14" t="n">
-        <v>121</v>
+        <v>275</v>
       </c>
       <c r="D14" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Furqan Ullah Khan</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373683</v>
+        <v>373716</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373716</v>
+        <v>373705</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Furqan Ullah Khan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373673</v>
+        <v>373683</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Muhammad Yousaf</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>373690</v>
+        <v>373673</v>
       </c>
       <c r="C18" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Muhammad Yousaf</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>373705</v>
+        <v>373690</v>
       </c>
       <c r="C19" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -979,39 +995,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>564273</v>
+        <v>373706</v>
       </c>
       <c r="C24" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="D24" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>373706</v>
+        <v>564273</v>
       </c>
       <c r="C25" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D25" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1081,13 +1097,13 @@
         <v>373710</v>
       </c>
       <c r="C29" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D29" t="n">
+        <v>30</v>
+      </c>
+      <c r="E29" t="n">
         <v>27</v>
-      </c>
-      <c r="E29" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -1150,36 +1166,36 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Anum Gul</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>373656</v>
+        <v>373669</v>
       </c>
       <c r="C33" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alia Khan</t>
+          <t>Anum Gul</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>373681</v>
+        <v>373656</v>
       </c>
       <c r="C34" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E34" t="n">
         <v>4</v>
@@ -1188,77 +1204,77 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nillum Bibi</t>
+          <t>Alia Khan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>373652</v>
+        <v>373681</v>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nazia</t>
+          <t>Nillum Bibi</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>373657</v>
+        <v>373652</v>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Nazia</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>373699</v>
+        <v>373657</v>
       </c>
       <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
         <v>6</v>
       </c>
-      <c r="D37" t="n">
-        <v>5</v>
-      </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>373669</v>
+        <v>373699</v>
       </c>
       <c r="C38" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2238</v>
+        <v>2133</v>
       </c>
       <c r="C2" t="n">
-        <v>2229</v>
+        <v>2120</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>589</v>
+        <v>673</v>
       </c>
       <c r="C4" t="n">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="D4" t="n">
-        <v>281</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1056</v>
+        <v>1277</v>
       </c>
       <c r="C5" t="n">
-        <v>254</v>
+        <v>355</v>
       </c>
       <c r="D5" t="n">
-        <v>802</v>
+        <v>922</v>
       </c>
     </row>
     <row r="6">
@@ -510,29 +510,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Girls vs Household</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -584,13 +568,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2238</v>
+        <v>2133</v>
       </c>
       <c r="D2" t="n">
-        <v>2229</v>
+        <v>2120</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -603,51 +587,51 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="D3" t="n">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373648</v>
+        <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D4" t="n">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373646</v>
+        <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="D5" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E5" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
@@ -660,13 +644,13 @@
         <v>373642</v>
       </c>
       <c r="C6" t="n">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="D6" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -679,13 +663,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="D7" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -748,77 +732,77 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373649</v>
+        <v>373651</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="D11" t="n">
+        <v>102</v>
+      </c>
+      <c r="E11" t="n">
         <v>96</v>
-      </c>
-      <c r="E11" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373691</v>
+        <v>373649</v>
       </c>
       <c r="C12" t="n">
-        <v>287</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E12" t="n">
-        <v>201</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373651</v>
+        <v>373705</v>
       </c>
       <c r="C13" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="D13" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373658</v>
+        <v>373691</v>
       </c>
       <c r="C14" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E14" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
@@ -831,32 +815,32 @@
         <v>373716</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373705</v>
+        <v>373658</v>
       </c>
       <c r="C16" t="n">
-        <v>105</v>
+        <v>275</v>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17">
@@ -919,96 +903,96 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jaweria</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>163495</v>
+        <v>373706</v>
       </c>
       <c r="C20" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Jaweria</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373671</v>
+        <v>163495</v>
       </c>
       <c r="C21" t="n">
+        <v>56</v>
+      </c>
+      <c r="D21" t="n">
         <v>55</v>
       </c>
-      <c r="D21" t="n">
-        <v>51</v>
-      </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>453925</v>
+        <v>373671</v>
       </c>
       <c r="C22" t="n">
+        <v>55</v>
+      </c>
+      <c r="D22" t="n">
         <v>51</v>
       </c>
-      <c r="D22" t="n">
-        <v>49</v>
-      </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Asma Gull</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>373672</v>
+        <v>453925</v>
       </c>
       <c r="C23" t="n">
         <v>51</v>
       </c>
       <c r="D23" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Asma Gull</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>373706</v>
+        <v>373672</v>
       </c>
       <c r="C24" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E24" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1033,77 +1017,77 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>373665</v>
+        <v>373710</v>
       </c>
       <c r="C26" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irum ikram</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>541376</v>
+        <v>373665</v>
       </c>
       <c r="C27" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Naureen</t>
+          <t>Irum ikram</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>884887</v>
+        <v>541376</v>
       </c>
       <c r="C28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D28" t="n">
         <v>31</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Naureen</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>373710</v>
+        <v>884887</v>
       </c>
       <c r="C29" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E29" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1128,58 +1112,58 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Munawar Khan</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>373668</v>
+        <v>373669</v>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lati khan</t>
+          <t>Munawar Khan</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>671211</v>
+        <v>373668</v>
       </c>
       <c r="C32" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Lati khan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>373669</v>
+        <v>671211</v>
       </c>
       <c r="C33" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E33" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,26 +414,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -454,64 +442,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Girls</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>589</v>
+        <v>3945</v>
       </c>
       <c r="C2" t="n">
-        <v>308</v>
+        <v>3693</v>
       </c>
       <c r="D2" t="n">
-        <v>281</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Tracking vs Household</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1056</v>
+        <v>2238</v>
       </c>
       <c r="C3" t="n">
-        <v>254</v>
+        <v>2229</v>
       </c>
       <c r="D3" t="n">
-        <v>802</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Household vs Girls</t>
+          <t>Girls</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>592</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>311</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Household</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1056</v>
+      </c>
+      <c r="C5" t="n">
+        <v>254</v>
+      </c>
+      <c r="D5" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Household vs Girls</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Girls vs Household</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -526,31 +546,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -559,305 +579,1101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kainat</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>373712</v>
-      </c>
+          <t>UNASSIGNED (Tracking vs Household)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>304</v>
+        <v>2238</v>
       </c>
       <c r="D2" t="n">
-        <v>103</v>
+        <v>2229</v>
       </c>
       <c r="E2" t="n">
-        <v>201</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Asma Bibi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>373692</v>
+        <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>283</v>
+        <v>358</v>
       </c>
       <c r="D3" t="n">
-        <v>101</v>
+        <v>299</v>
       </c>
       <c r="E3" t="n">
-        <v>182</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373691</v>
+        <v>373684</v>
       </c>
       <c r="C4" t="n">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="E4" t="n">
-        <v>200</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373658</v>
+        <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="E5" t="n">
-        <v>194</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Asma Bibi</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373641</v>
+        <v>373696</v>
       </c>
       <c r="C6" t="n">
-        <v>84</v>
+        <v>249</v>
       </c>
       <c r="D6" t="n">
-        <v>47</v>
+        <v>224</v>
       </c>
       <c r="E6" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373648</v>
+        <v>373646</v>
       </c>
       <c r="C7" t="n">
-        <v>76</v>
+        <v>251</v>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>215</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373651</v>
+        <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>92</v>
+        <v>240</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>211</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373642</v>
+        <v>373649</v>
       </c>
       <c r="C9" t="n">
-        <v>48</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373705</v>
+        <v>373673</v>
       </c>
       <c r="C10" t="n">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373669</v>
+        <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373646</v>
+        <v>373651</v>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373716</v>
+        <v>373712</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>333</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373706</v>
+        <v>373716</v>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>124</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373696</v>
+        <v>373671</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Furqan Ullah Khan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>453925</v>
+        <v>373683</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Zohra</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>373692</v>
+      </c>
+      <c r="C17" t="n">
+        <v>298</v>
+      </c>
+      <c r="D17" t="n">
+        <v>115</v>
+      </c>
+      <c r="E17" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Asma Gull</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>373672</v>
+      </c>
+      <c r="C18" t="n">
+        <v>109</v>
+      </c>
+      <c r="D18" t="n">
+        <v>105</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Samara</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>373658</v>
+      </c>
+      <c r="C19" t="n">
+        <v>298</v>
+      </c>
+      <c r="D19" t="n">
+        <v>102</v>
+      </c>
+      <c r="E19" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ishaq Khan</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>373699</v>
+      </c>
+      <c r="C20" t="n">
+        <v>101</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Muhammad Yousaf</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>373690</v>
+      </c>
+      <c r="C21" t="n">
+        <v>105</v>
+      </c>
+      <c r="D21" t="n">
+        <v>96</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rehana Bibi</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>373691</v>
+      </c>
+      <c r="C22" t="n">
+        <v>295</v>
+      </c>
+      <c r="D22" t="n">
+        <v>94</v>
+      </c>
+      <c r="E22" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lati Khan</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>564273</v>
+      </c>
+      <c r="C23" t="n">
+        <v>98</v>
+      </c>
+      <c r="D23" t="n">
+        <v>94</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Naureen khan</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>453925</v>
+      </c>
+      <c r="C24" t="n">
+        <v>92</v>
+      </c>
+      <c r="D24" t="n">
+        <v>90</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Laiba Shams</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>373706</v>
+      </c>
+      <c r="C25" t="n">
+        <v>115</v>
+      </c>
+      <c r="D25" t="n">
+        <v>87</v>
+      </c>
+      <c r="E25" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Irum ikram</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>541376</v>
+      </c>
+      <c r="C26" t="n">
+        <v>88</v>
+      </c>
+      <c r="D26" t="n">
+        <v>83</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lati Khan</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>373665</v>
+      </c>
+      <c r="C27" t="n">
+        <v>86</v>
+      </c>
+      <c r="D27" t="n">
+        <v>83</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Naureen</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>884887</v>
+      </c>
+      <c r="C28" t="n">
+        <v>86</v>
+      </c>
+      <c r="D28" t="n">
+        <v>82</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Jaweria</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>163495</v>
+      </c>
+      <c r="C29" t="n">
+        <v>83</v>
+      </c>
+      <c r="D29" t="n">
+        <v>82</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Nillum Bibi</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>373652</v>
+      </c>
+      <c r="C30" t="n">
+        <v>64</v>
+      </c>
+      <c r="D30" t="n">
+        <v>61</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Anum Gul</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>373656</v>
+      </c>
+      <c r="C31" t="n">
+        <v>55</v>
+      </c>
+      <c r="D31" t="n">
+        <v>51</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Muniba Shamim</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>373659</v>
+      </c>
+      <c r="C32" t="n">
+        <v>58</v>
+      </c>
+      <c r="D32" t="n">
+        <v>49</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Nazia</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>373657</v>
+      </c>
+      <c r="C33" t="n">
+        <v>51</v>
+      </c>
+      <c r="D33" t="n">
+        <v>49</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Alia Khan</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>373681</v>
+      </c>
+      <c r="C34" t="n">
+        <v>44</v>
+      </c>
+      <c r="D34" t="n">
+        <v>40</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Lati khan</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>671211</v>
+      </c>
+      <c r="C35" t="n">
+        <v>38</v>
+      </c>
+      <c r="D35" t="n">
+        <v>38</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Summiya Hayat</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B36" t="n">
         <v>373710</v>
       </c>
-      <c r="C17" t="n">
-        <v>17</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C36" t="n">
+        <v>60</v>
+      </c>
+      <c r="D36" t="n">
+        <v>33</v>
+      </c>
+      <c r="E36" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Munawar Khan</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>373668</v>
+      </c>
+      <c r="C37" t="n">
+        <v>39</v>
+      </c>
+      <c r="D37" t="n">
+        <v>33</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Laiba Khan</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>373653</v>
+      </c>
+      <c r="C38" t="n">
+        <v>26</v>
+      </c>
+      <c r="D38" t="n">
+        <v>22</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chashm Gul</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>373695</v>
+      </c>
+      <c r="C39" t="n">
+        <v>27</v>
+      </c>
+      <c r="D39" t="n">
+        <v>18</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nadia bibi</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>373669</v>
+      </c>
+      <c r="C40" t="n">
+        <v>41</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Zain Ul Abideen</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>373667</v>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="n">
+        <v>12</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lati khan</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>652938</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Saba Ramzan</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>373703</v>
+      </c>
+      <c r="C43" t="n">
+        <v>9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Shehla Noor</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>373650</v>
+      </c>
+      <c r="C44" t="n">
+        <v>9</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Muhammad naeem</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>571571</v>
+      </c>
+      <c r="C45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sadia rustum</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>852541</v>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Usman Ali</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>373687</v>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Muhammad Noor</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>373701</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="n">
         <v>3</v>
       </c>
-      <c r="E17" t="n">
-        <v>14</v>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Muhammad Naeem</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>373694</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Muhammad Shahid Khan</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>373662</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sajjad Khan</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>373700</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Aisha Aman</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>373704</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Rahila Naaz</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>373715</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Robina Shaheen</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>373639</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Iqra Bibi</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>373708</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Mahnoorr</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>373670</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gul Rukh</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>373644</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Hijab Zahra</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>373637</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sidra Khan</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>373645</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,22 +430,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -446,10 +458,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3945</v>
+        <v>3936</v>
       </c>
       <c r="C2" t="n">
-        <v>3693</v>
+        <v>3684</v>
       </c>
       <c r="D2" t="n">
         <v>252</v>
@@ -478,10 +490,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C4" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D4" t="n">
         <v>281</v>
@@ -550,27 +562,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -603,10 +615,10 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D3" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E3" t="n">
         <v>59</v>
@@ -717,10 +729,10 @@
         <v>373649</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
@@ -748,39 +760,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373705</v>
+        <v>373651</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373651</v>
+        <v>373705</v>
       </c>
       <c r="C12" t="n">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -983,10 +995,10 @@
         <v>564273</v>
       </c>
       <c r="C23" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
@@ -1249,10 +1261,10 @@
         <v>373668</v>
       </c>
       <c r="C37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D37" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E37" t="n">
         <v>6</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,22 +418,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -562,27 +550,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,26 +414,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -454,17 +442,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3936</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3684</v>
+      </c>
+      <c r="D2" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tracking vs Household</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2238</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2229</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Girls</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B4" t="n">
         <v>590</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C4" t="n">
         <v>309</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D4" t="n">
         <v>281</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Household</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1052</v>
+      </c>
+      <c r="C5" t="n">
+        <v>250</v>
+      </c>
+      <c r="D5" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Household vs Girls</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Girls vs Household</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -478,31 +546,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -511,304 +579,1100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kainat</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>373712</v>
-      </c>
+          <t>UNASSIGNED (Tracking vs Household)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>129</v>
+        <v>2238</v>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>2229</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Asma Bibi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>373692</v>
+        <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>106</v>
+        <v>356</v>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
+        <v>297</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373658</v>
+        <v>373684</v>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>293</v>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>265</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373691</v>
+        <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>106</v>
+        <v>330</v>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>260</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Asma Bibi</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373641</v>
+        <v>373696</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>249</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>224</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373648</v>
+        <v>373646</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>250</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>214</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373705</v>
+        <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>211</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373651</v>
+        <v>373649</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>192</v>
       </c>
       <c r="D9" t="n">
+        <v>182</v>
+      </c>
+      <c r="E9" t="n">
         <v>10</v>
-      </c>
-      <c r="E9" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373669</v>
+        <v>373673</v>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373642</v>
+        <v>373651</v>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>214</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373646</v>
+        <v>373705</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373716</v>
+        <v>373712</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>333</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>131</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373706</v>
+        <v>373716</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>453925</v>
+        <v>373671</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="D15" t="n">
+        <v>122</v>
+      </c>
+      <c r="E15" t="n">
         <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Furqan Ullah Khan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373696</v>
+        <v>373683</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Zohra</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>373692</v>
+      </c>
+      <c r="C17" t="n">
+        <v>298</v>
+      </c>
+      <c r="D17" t="n">
+        <v>115</v>
+      </c>
+      <c r="E17" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Asma Gull</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>373672</v>
+      </c>
+      <c r="C18" t="n">
+        <v>109</v>
+      </c>
+      <c r="D18" t="n">
+        <v>105</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Samara</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>373658</v>
+      </c>
+      <c r="C19" t="n">
+        <v>298</v>
+      </c>
+      <c r="D19" t="n">
+        <v>102</v>
+      </c>
+      <c r="E19" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ishaq Khan</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>373699</v>
+      </c>
+      <c r="C20" t="n">
+        <v>101</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Muhammad Yousaf</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>373690</v>
+      </c>
+      <c r="C21" t="n">
+        <v>105</v>
+      </c>
+      <c r="D21" t="n">
+        <v>96</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rehana Bibi</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>373691</v>
+      </c>
+      <c r="C22" t="n">
+        <v>295</v>
+      </c>
+      <c r="D22" t="n">
+        <v>94</v>
+      </c>
+      <c r="E22" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lati Khan</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>564273</v>
+      </c>
+      <c r="C23" t="n">
+        <v>97</v>
+      </c>
+      <c r="D23" t="n">
+        <v>93</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Naureen khan</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>453925</v>
+      </c>
+      <c r="C24" t="n">
+        <v>91</v>
+      </c>
+      <c r="D24" t="n">
+        <v>89</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Laiba Shams</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>373706</v>
+      </c>
+      <c r="C25" t="n">
+        <v>114</v>
+      </c>
+      <c r="D25" t="n">
+        <v>86</v>
+      </c>
+      <c r="E25" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Irum ikram</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>541376</v>
+      </c>
+      <c r="C26" t="n">
+        <v>88</v>
+      </c>
+      <c r="D26" t="n">
+        <v>83</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lati Khan</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>373665</v>
+      </c>
+      <c r="C27" t="n">
+        <v>86</v>
+      </c>
+      <c r="D27" t="n">
+        <v>83</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Naureen</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>884887</v>
+      </c>
+      <c r="C28" t="n">
+        <v>86</v>
+      </c>
+      <c r="D28" t="n">
+        <v>82</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Jaweria</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>163495</v>
+      </c>
+      <c r="C29" t="n">
+        <v>83</v>
+      </c>
+      <c r="D29" t="n">
+        <v>82</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Nillum Bibi</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>373652</v>
+      </c>
+      <c r="C30" t="n">
+        <v>64</v>
+      </c>
+      <c r="D30" t="n">
+        <v>61</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Anum Gul</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>373656</v>
+      </c>
+      <c r="C31" t="n">
+        <v>55</v>
+      </c>
+      <c r="D31" t="n">
+        <v>51</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Muniba Shamim</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>373659</v>
+      </c>
+      <c r="C32" t="n">
+        <v>58</v>
+      </c>
+      <c r="D32" t="n">
+        <v>49</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Nazia</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>373657</v>
+      </c>
+      <c r="C33" t="n">
+        <v>51</v>
+      </c>
+      <c r="D33" t="n">
+        <v>49</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Alia Khan</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>373681</v>
+      </c>
+      <c r="C34" t="n">
+        <v>44</v>
+      </c>
+      <c r="D34" t="n">
+        <v>40</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Lati khan</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>671211</v>
+      </c>
+      <c r="C35" t="n">
+        <v>38</v>
+      </c>
+      <c r="D35" t="n">
+        <v>38</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Summiya Hayat</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B36" t="n">
         <v>373710</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C36" t="n">
+        <v>60</v>
+      </c>
+      <c r="D36" t="n">
+        <v>33</v>
+      </c>
+      <c r="E36" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Munawar Khan</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>373668</v>
+      </c>
+      <c r="C37" t="n">
+        <v>38</v>
+      </c>
+      <c r="D37" t="n">
+        <v>32</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Laiba Khan</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>373653</v>
+      </c>
+      <c r="C38" t="n">
+        <v>26</v>
+      </c>
+      <c r="D38" t="n">
+        <v>22</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chashm Gul</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>373695</v>
+      </c>
+      <c r="C39" t="n">
+        <v>27</v>
+      </c>
+      <c r="D39" t="n">
+        <v>18</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nadia bibi</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>373669</v>
+      </c>
+      <c r="C40" t="n">
+        <v>41</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Zain Ul Abideen</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>373667</v>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="n">
+        <v>12</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lati khan</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>652938</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Saba Ramzan</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>373703</v>
+      </c>
+      <c r="C43" t="n">
+        <v>9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Shehla Noor</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>373650</v>
+      </c>
+      <c r="C44" t="n">
+        <v>9</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Muhammad naeem</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>571571</v>
+      </c>
+      <c r="C45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="n">
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sadia rustum</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>852541</v>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Usman Ali</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>373687</v>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Muhammad Noor</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>373701</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Muhammad Naeem</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>373694</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Muhammad Shahid Khan</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>373662</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sajjad Khan</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>373700</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Aisha Aman</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>373704</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Rahila Naaz</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>373715</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Robina Shaheen</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>373639</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Iqra Bibi</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>373708</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Mahnoorr</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>373670</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gul Rukh</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>373644</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Hijab Zahra</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>373637</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sidra Khan</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>373645</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,22 +430,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -550,27 +562,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="by_enumerator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,22 +418,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -490,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C4" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D4" t="n">
         <v>281</v>
@@ -506,10 +494,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="C5" t="n">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D5" t="n">
         <v>802</v>
@@ -562,27 +550,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -615,10 +603,10 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D3" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E3" t="n">
         <v>59</v>
@@ -653,10 +641,10 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D5" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E5" t="n">
         <v>70</v>
@@ -710,10 +698,10 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D8" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E8" t="n">
         <v>29</v>
@@ -881,10 +869,10 @@
         <v>373692</v>
       </c>
       <c r="C17" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E17" t="n">
         <v>183</v>
@@ -969,39 +957,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>373691</v>
+        <v>564273</v>
       </c>
       <c r="C22" t="n">
-        <v>295</v>
+        <v>97</v>
       </c>
       <c r="D22" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E22" t="n">
-        <v>201</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>564273</v>
+        <v>373691</v>
       </c>
       <c r="C23" t="n">
-        <v>97</v>
+        <v>293</v>
       </c>
       <c r="D23" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C4" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D4" t="n">
         <v>281</v>
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="C5" t="n">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D5" t="n">
         <v>802</v>
@@ -603,10 +603,10 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D3" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E3" t="n">
         <v>59</v>
@@ -641,10 +641,10 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D5" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E5" t="n">
         <v>70</v>
@@ -698,10 +698,10 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D8" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E8" t="n">
         <v>29</v>
@@ -983,10 +983,10 @@
         <v>373691</v>
       </c>
       <c r="C23" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D23" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E23" t="n">
         <v>201</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,65 +442,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Girls</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>583</v>
+        <v>3936</v>
       </c>
       <c r="C2" t="n">
-        <v>302</v>
+        <v>3684</v>
       </c>
       <c r="D2" t="n">
-        <v>281</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Tracking vs Household</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1038</v>
+        <v>2133</v>
       </c>
       <c r="C3" t="n">
-        <v>236</v>
+        <v>2120</v>
       </c>
       <c r="D3" t="n">
-        <v>802</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Household vs Girls</t>
+          <t>Girls</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>665</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>353</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Girls vs Household</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>1248</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>922</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Household vs Girls</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -514,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,305 +563,1101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kainat</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>373712</v>
-      </c>
+          <t>UNASSIGNED (Tracking vs Household)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>305</v>
+        <v>2133</v>
       </c>
       <c r="D2" t="n">
-        <v>104</v>
+        <v>2120</v>
       </c>
       <c r="E2" t="n">
-        <v>201</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Asma Bibi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>373692</v>
+        <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>280</v>
+        <v>396</v>
       </c>
       <c r="D3" t="n">
-        <v>98</v>
+        <v>323</v>
       </c>
       <c r="E3" t="n">
-        <v>182</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373691</v>
+        <v>373684</v>
       </c>
       <c r="C4" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="E4" t="n">
-        <v>200</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373658</v>
+        <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>270</v>
+        <v>343</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>258</v>
       </c>
       <c r="E5" t="n">
-        <v>194</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Asma Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373641</v>
+        <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="D6" t="n">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="E6" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373651</v>
+        <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>92</v>
+        <v>280</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>235</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373648</v>
+        <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>72</v>
+        <v>258</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>218</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373705</v>
+        <v>373649</v>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>182</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373642</v>
+        <v>373651</v>
       </c>
       <c r="C10" t="n">
-        <v>42</v>
+        <v>247</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373669</v>
+        <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>41</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373716</v>
+        <v>373673</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373646</v>
+        <v>373716</v>
       </c>
       <c r="C13" t="n">
-        <v>32</v>
+        <v>161</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373706</v>
+        <v>373712</v>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>333</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373696</v>
+        <v>373671</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Furqan Ullah Khan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>453925</v>
+        <v>373683</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Zohra</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>373692</v>
+      </c>
+      <c r="C17" t="n">
+        <v>295</v>
+      </c>
+      <c r="D17" t="n">
+        <v>112</v>
+      </c>
+      <c r="E17" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Asma Gull</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>373672</v>
+      </c>
+      <c r="C18" t="n">
+        <v>109</v>
+      </c>
+      <c r="D18" t="n">
+        <v>105</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Samara</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>373658</v>
+      </c>
+      <c r="C19" t="n">
+        <v>298</v>
+      </c>
+      <c r="D19" t="n">
+        <v>102</v>
+      </c>
+      <c r="E19" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ishaq Khan</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>373699</v>
+      </c>
+      <c r="C20" t="n">
+        <v>101</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Muhammad Yousaf</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>373690</v>
+      </c>
+      <c r="C21" t="n">
+        <v>105</v>
+      </c>
+      <c r="D21" t="n">
+        <v>96</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Laiba Shams</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>373706</v>
+      </c>
+      <c r="C22" t="n">
+        <v>131</v>
+      </c>
+      <c r="D22" t="n">
+        <v>95</v>
+      </c>
+      <c r="E22" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lati Khan</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>564273</v>
+      </c>
+      <c r="C23" t="n">
+        <v>97</v>
+      </c>
+      <c r="D23" t="n">
+        <v>93</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Rehana Bibi</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>373691</v>
+      </c>
+      <c r="C24" t="n">
+        <v>291</v>
+      </c>
+      <c r="D24" t="n">
+        <v>90</v>
+      </c>
+      <c r="E24" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Naureen khan</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>453925</v>
+      </c>
+      <c r="C25" t="n">
+        <v>91</v>
+      </c>
+      <c r="D25" t="n">
+        <v>89</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Irum ikram</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>541376</v>
+      </c>
+      <c r="C26" t="n">
+        <v>88</v>
+      </c>
+      <c r="D26" t="n">
+        <v>83</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lati Khan</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>373665</v>
+      </c>
+      <c r="C27" t="n">
+        <v>86</v>
+      </c>
+      <c r="D27" t="n">
+        <v>83</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Naureen</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>884887</v>
+      </c>
+      <c r="C28" t="n">
+        <v>86</v>
+      </c>
+      <c r="D28" t="n">
+        <v>82</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Jaweria</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>163495</v>
+      </c>
+      <c r="C29" t="n">
+        <v>83</v>
+      </c>
+      <c r="D29" t="n">
+        <v>82</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Nillum Bibi</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>373652</v>
+      </c>
+      <c r="C30" t="n">
+        <v>64</v>
+      </c>
+      <c r="D30" t="n">
+        <v>61</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Anum Gul</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>373656</v>
+      </c>
+      <c r="C31" t="n">
+        <v>55</v>
+      </c>
+      <c r="D31" t="n">
+        <v>51</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Muniba Shamim</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>373659</v>
+      </c>
+      <c r="C32" t="n">
+        <v>58</v>
+      </c>
+      <c r="D32" t="n">
+        <v>49</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Nazia</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>373657</v>
+      </c>
+      <c r="C33" t="n">
+        <v>51</v>
+      </c>
+      <c r="D33" t="n">
+        <v>49</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Summiya Hayat</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B34" t="n">
         <v>373710</v>
       </c>
-      <c r="C17" t="n">
-        <v>17</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C34" t="n">
+        <v>71</v>
+      </c>
+      <c r="D34" t="n">
+        <v>40</v>
+      </c>
+      <c r="E34" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Alia Khan</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>373681</v>
+      </c>
+      <c r="C35" t="n">
+        <v>44</v>
+      </c>
+      <c r="D35" t="n">
+        <v>40</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Lati khan</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>671211</v>
+      </c>
+      <c r="C36" t="n">
+        <v>38</v>
+      </c>
+      <c r="D36" t="n">
+        <v>38</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Munawar Khan</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>373668</v>
+      </c>
+      <c r="C37" t="n">
+        <v>38</v>
+      </c>
+      <c r="D37" t="n">
+        <v>32</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Laiba Khan</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>373653</v>
+      </c>
+      <c r="C38" t="n">
+        <v>26</v>
+      </c>
+      <c r="D38" t="n">
+        <v>22</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Nadia bibi</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>373669</v>
+      </c>
+      <c r="C39" t="n">
+        <v>54</v>
+      </c>
+      <c r="D39" t="n">
+        <v>21</v>
+      </c>
+      <c r="E39" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chashm Gul</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>373695</v>
+      </c>
+      <c r="C40" t="n">
+        <v>27</v>
+      </c>
+      <c r="D40" t="n">
+        <v>18</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Zain Ul Abideen</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>373667</v>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="n">
+        <v>12</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lati khan</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>652938</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Saba Ramzan</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>373703</v>
+      </c>
+      <c r="C43" t="n">
+        <v>9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Shehla Noor</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>373650</v>
+      </c>
+      <c r="C44" t="n">
+        <v>9</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Muhammad naeem</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>571571</v>
+      </c>
+      <c r="C45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sadia rustum</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>852541</v>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Usman Ali</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>373687</v>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Muhammad Noor</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>373701</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="n">
         <v>3</v>
       </c>
-      <c r="E17" t="n">
-        <v>14</v>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Muhammad Naeem</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>373694</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Muhammad Shahid Khan</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>373662</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sajjad Khan</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>373700</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Aisha Aman</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>373704</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Rahila Naaz</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>373715</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Robina Shaheen</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>373639</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Iqra Bibi</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>373708</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Mahnoorr</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>373670</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gul Rukh</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>373644</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Hijab Zahra</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>373637</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sidra Khan</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>373645</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C4" t="n">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D4" t="n">
         <v>312</v>
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1248</v>
+        <v>1241</v>
       </c>
       <c r="C5" t="n">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D5" t="n">
         <v>922</v>
@@ -625,10 +625,10 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D5" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E5" t="n">
         <v>85</v>
@@ -663,10 +663,10 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D7" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
@@ -720,10 +720,10 @@
         <v>373651</v>
       </c>
       <c r="C10" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D10" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E10" t="n">
         <v>96</v>
@@ -796,10 +796,10 @@
         <v>373712</v>
       </c>
       <c r="C14" t="n">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D14" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E14" t="n">
         <v>202</v>
@@ -853,10 +853,10 @@
         <v>373692</v>
       </c>
       <c r="C17" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D17" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E17" t="n">
         <v>183</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="C5" t="n">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D5" t="n">
         <v>922</v>
@@ -625,10 +625,10 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D5" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E5" t="n">
         <v>85</v>
@@ -853,10 +853,10 @@
         <v>373692</v>
       </c>
       <c r="C17" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D17" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E17" t="n">
         <v>183</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -462,13 +462,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2133</v>
+        <v>2075</v>
       </c>
       <c r="C3" t="n">
-        <v>2120</v>
+        <v>2060</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>661</v>
+        <v>709</v>
       </c>
       <c r="C4" t="n">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="D4" t="n">
-        <v>312</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1237</v>
+        <v>1316</v>
       </c>
       <c r="C5" t="n">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="D5" t="n">
-        <v>922</v>
+        <v>984</v>
       </c>
     </row>
     <row r="6">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -568,13 +568,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2133</v>
+        <v>2075</v>
       </c>
       <c r="D2" t="n">
-        <v>2120</v>
+        <v>2060</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -587,13 +587,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="D3" t="n">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
@@ -625,13 +625,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="D5" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -644,13 +644,13 @@
         <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -663,13 +663,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
         <v>233</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -682,13 +682,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="D8" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -713,39 +713,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373651</v>
+        <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>245</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373705</v>
+        <v>373651</v>
       </c>
       <c r="C11" t="n">
-        <v>196</v>
+        <v>259</v>
       </c>
       <c r="D11" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -777,13 +777,13 @@
         <v>373716</v>
       </c>
       <c r="C13" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D13" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -1226,58 +1226,58 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Munawar Khan</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>373668</v>
+        <v>373669</v>
       </c>
       <c r="C37" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D37" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Laiba Khan</t>
+          <t>Munawar Khan</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>373653</v>
+        <v>373668</v>
       </c>
       <c r="C38" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D38" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Laiba Khan</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>373669</v>
+        <v>373653</v>
       </c>
       <c r="C39" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E39" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="C5" t="n">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D5" t="n">
         <v>984</v>
@@ -625,10 +625,10 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D5" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E5" t="n">
         <v>98</v>
@@ -644,10 +644,10 @@
         <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D6" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E6" t="n">
         <v>67</v>
@@ -663,10 +663,10 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E7" t="n">
         <v>62</v>
@@ -682,10 +682,10 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E8" t="n">
         <v>48</v>
@@ -777,10 +777,10 @@
         <v>373716</v>
       </c>
       <c r="C13" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D13" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E13" t="n">
         <v>31</v>
@@ -853,10 +853,10 @@
         <v>373692</v>
       </c>
       <c r="C17" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D17" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E17" t="n">
         <v>183</v>
@@ -891,10 +891,10 @@
         <v>373658</v>
       </c>
       <c r="C19" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D19" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E19" t="n">
         <v>196</v>
@@ -1207,39 +1207,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lati khan</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>671211</v>
+        <v>373669</v>
       </c>
       <c r="C36" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="D36" t="n">
         <v>38</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Lati khan</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>373669</v>
+        <v>671211</v>
       </c>
       <c r="C37" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,26 +426,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Survey</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -462,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2075</v>
+        <v>1985</v>
       </c>
       <c r="C3" t="n">
-        <v>2060</v>
+        <v>1969</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>709</v>
+        <v>756</v>
       </c>
       <c r="C4" t="n">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="D4" t="n">
-        <v>331</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5">
@@ -494,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1324</v>
+        <v>1402</v>
       </c>
       <c r="C5" t="n">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="D5" t="n">
-        <v>984</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="6">
@@ -510,13 +522,29 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Girls vs Household</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -534,27 +562,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Enumerator Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Enumerator ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Total Issues</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Critical Issues</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Flag Issues</t>
         </is>
@@ -568,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2075</v>
+        <v>1985</v>
       </c>
       <c r="D2" t="n">
-        <v>2060</v>
+        <v>1969</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -587,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="D3" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4">
@@ -625,13 +653,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D5" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E5" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
@@ -644,13 +672,13 @@
         <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="D6" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -663,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="D7" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -682,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -720,13 +748,13 @@
         <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -739,13 +767,13 @@
         <v>373651</v>
       </c>
       <c r="C11" t="n">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D11" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E11" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12">
@@ -865,96 +893,96 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Asma Gull</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>373672</v>
+        <v>373706</v>
       </c>
       <c r="C18" t="n">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="D18" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Asma Gull</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>373658</v>
+        <v>373672</v>
       </c>
       <c r="C19" t="n">
-        <v>299</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E19" t="n">
-        <v>196</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373699</v>
+        <v>373658</v>
       </c>
       <c r="C20" t="n">
-        <v>101</v>
+        <v>299</v>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Muhammad Yousaf</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373690</v>
+        <v>373699</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D21" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Muhammad Yousaf</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>373706</v>
+        <v>373690</v>
       </c>
       <c r="C22" t="n">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="D22" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E22" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1112,115 +1140,115 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Anum Gul</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>373656</v>
+        <v>373710</v>
       </c>
       <c r="C31" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="D31" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Muniba Shamim</t>
+          <t>Anum Gul</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>373659</v>
+        <v>373656</v>
       </c>
       <c r="C32" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D32" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nazia</t>
+          <t>Muniba Shamim</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>373657</v>
+        <v>373659</v>
       </c>
       <c r="C33" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D33" t="n">
         <v>49</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Nazia</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>373710</v>
+        <v>373657</v>
       </c>
       <c r="C34" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E34" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alia Khan</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>373681</v>
+        <v>373669</v>
       </c>
       <c r="C35" t="n">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="D35" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Alia Khan</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>373669</v>
+        <v>373681</v>
       </c>
       <c r="C36" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="D36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1985</v>
+        <v>1958</v>
       </c>
       <c r="C3" t="n">
-        <v>1969</v>
+        <v>1940</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>756</v>
+        <v>787</v>
       </c>
       <c r="C4" t="n">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="D4" t="n">
-        <v>350</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1402</v>
+        <v>1446</v>
       </c>
       <c r="C5" t="n">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="D5" t="n">
-        <v>1033</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1985</v>
+        <v>1958</v>
       </c>
       <c r="D2" t="n">
-        <v>1969</v>
+        <v>1940</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="D3" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4">
@@ -653,13 +653,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D5" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E5" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D6" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -691,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D7" t="n">
         <v>235</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -767,13 +767,13 @@
         <v>373651</v>
       </c>
       <c r="C11" t="n">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E11" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12">
@@ -805,13 +805,13 @@
         <v>373716</v>
       </c>
       <c r="C13" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D13" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E13" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -874,39 +874,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373692</v>
+        <v>373706</v>
       </c>
       <c r="C17" t="n">
-        <v>291</v>
+        <v>154</v>
       </c>
       <c r="D17" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E17" t="n">
-        <v>183</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>373706</v>
+        <v>373692</v>
       </c>
       <c r="C18" t="n">
-        <v>149</v>
+        <v>291</v>
       </c>
       <c r="D18" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19">
@@ -1147,13 +1147,13 @@
         <v>373710</v>
       </c>
       <c r="C31" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E31" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32">
@@ -1223,13 +1223,13 @@
         <v>373669</v>
       </c>
       <c r="C35" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D35" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E35" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1958</v>
+        <v>1917</v>
       </c>
       <c r="C3" t="n">
-        <v>1940</v>
+        <v>1898</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>787</v>
+        <v>820</v>
       </c>
       <c r="C4" t="n">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="D4" t="n">
-        <v>368</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1446</v>
+        <v>1525</v>
       </c>
       <c r="C5" t="n">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="D5" t="n">
-        <v>1068</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="6">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1958</v>
+        <v>1917</v>
       </c>
       <c r="D2" t="n">
-        <v>1940</v>
+        <v>1898</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -615,51 +615,51 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="D3" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373684</v>
+        <v>373648</v>
       </c>
       <c r="C4" t="n">
-        <v>293</v>
+        <v>375</v>
       </c>
       <c r="D4" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373648</v>
+        <v>373684</v>
       </c>
       <c r="C5" t="n">
-        <v>368</v>
+        <v>293</v>
       </c>
       <c r="D5" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E5" t="n">
-        <v>105</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D6" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -691,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="D7" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D8" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -741,39 +741,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373705</v>
+        <v>373651</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E10" t="n">
-        <v>56</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373651</v>
+        <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>283</v>
+        <v>224</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E11" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -881,13 +881,13 @@
         <v>373706</v>
       </c>
       <c r="C17" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D17" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
@@ -1121,39 +1121,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nillum Bibi</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>373652</v>
+        <v>373710</v>
       </c>
       <c r="C30" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Nillum Bibi</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>373710</v>
+        <v>373652</v>
       </c>
       <c r="C31" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="D31" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1223,13 +1223,13 @@
         <v>373669</v>
       </c>
       <c r="C35" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D35" t="n">
         <v>45</v>
       </c>
       <c r="E35" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1917</v>
+        <v>1863</v>
       </c>
       <c r="C3" t="n">
-        <v>1898</v>
+        <v>1844</v>
       </c>
       <c r="D3" t="n">
         <v>19</v>
@@ -596,10 +596,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1917</v>
+        <v>1863</v>
       </c>
       <c r="D2" t="n">
-        <v>1898</v>
+        <v>1844</v>
       </c>
       <c r="E2" t="n">
         <v>19</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>820</v>
+        <v>773</v>
       </c>
       <c r="C4" t="n">
         <v>438</v>
       </c>
       <c r="D4" t="n">
-        <v>382</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D3" t="n">
         <v>353</v>
       </c>
       <c r="E3" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4">
@@ -672,13 +672,13 @@
         <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D6" t="n">
         <v>250</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
         <v>232</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>373651</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
       </c>
       <c r="E10" t="n">
-        <v>143</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -767,13 +767,13 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D11" t="n">
         <v>164</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -881,13 +881,13 @@
         <v>373706</v>
       </c>
       <c r="C17" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D17" t="n">
         <v>111</v>
       </c>
       <c r="E17" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
@@ -900,13 +900,13 @@
         <v>373692</v>
       </c>
       <c r="C18" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D18" t="n">
         <v>108</v>
       </c>
       <c r="E18" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19">
@@ -1128,13 +1128,13 @@
         <v>373710</v>
       </c>
       <c r="C30" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D30" t="n">
         <v>62</v>
       </c>
       <c r="E30" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
@@ -1223,13 +1223,13 @@
         <v>373669</v>
       </c>
       <c r="C35" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D35" t="n">
         <v>45</v>
       </c>
       <c r="E35" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1525</v>
+        <v>1514</v>
       </c>
       <c r="C5" t="n">
         <v>398</v>
       </c>
       <c r="D5" t="n">
-        <v>1127</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D6" t="n">
         <v>250</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
         <v>232</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>373651</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
       </c>
       <c r="E10" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -824,13 +824,13 @@
         <v>373712</v>
       </c>
       <c r="C14" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D14" t="n">
         <v>129</v>
       </c>
       <c r="E14" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
@@ -900,13 +900,13 @@
         <v>373692</v>
       </c>
       <c r="C18" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D18" t="n">
         <v>108</v>
       </c>
       <c r="E18" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19">
@@ -938,13 +938,13 @@
         <v>373658</v>
       </c>
       <c r="C20" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D20" t="n">
         <v>103</v>
       </c>
       <c r="E20" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21">
@@ -1014,13 +1014,13 @@
         <v>373691</v>
       </c>
       <c r="C24" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D24" t="n">
         <v>90</v>
       </c>
       <c r="E24" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1514</v>
+        <v>1480</v>
       </c>
       <c r="C5" t="n">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="D5" t="n">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="6">
@@ -615,10 +615,10 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D3" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E3" t="n">
         <v>110</v>
@@ -627,39 +627,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373648</v>
+        <v>373684</v>
       </c>
       <c r="C4" t="n">
-        <v>375</v>
+        <v>293</v>
       </c>
       <c r="D4" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373684</v>
+        <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>293</v>
+        <v>372</v>
       </c>
       <c r="D5" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6">
@@ -672,10 +672,10 @@
         <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D6" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E6" t="n">
         <v>82</v>
@@ -691,10 +691,10 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D7" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E7" t="n">
         <v>94</v>
@@ -710,10 +710,10 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E8" t="n">
         <v>51</v>
@@ -748,10 +748,10 @@
         <v>373651</v>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E10" t="n">
         <v>122</v>
@@ -767,10 +767,10 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E11" t="n">
         <v>52</v>
@@ -881,10 +881,10 @@
         <v>373706</v>
       </c>
       <c r="C17" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D17" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E17" t="n">
         <v>42</v>
@@ -893,77 +893,77 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Asma Gull</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>373692</v>
+        <v>373672</v>
       </c>
       <c r="C18" t="n">
-        <v>289</v>
+        <v>109</v>
       </c>
       <c r="D18" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E18" t="n">
-        <v>181</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Asma Gull</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>373672</v>
+        <v>373692</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>283</v>
       </c>
       <c r="D19" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373658</v>
+        <v>373699</v>
       </c>
       <c r="C20" t="n">
-        <v>297</v>
+        <v>101</v>
       </c>
       <c r="D20" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>194</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373699</v>
+        <v>373658</v>
       </c>
       <c r="C21" t="n">
-        <v>101</v>
+        <v>293</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22">
@@ -1007,39 +1007,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>373691</v>
+        <v>453925</v>
       </c>
       <c r="C24" t="n">
-        <v>289</v>
+        <v>91</v>
       </c>
       <c r="D24" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" t="n">
-        <v>199</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>453925</v>
+        <v>373691</v>
       </c>
       <c r="C25" t="n">
-        <v>91</v>
+        <v>288</v>
       </c>
       <c r="D25" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26">
@@ -1128,10 +1128,10 @@
         <v>373710</v>
       </c>
       <c r="C30" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30" t="n">
         <v>35</v>
@@ -1223,10 +1223,10 @@
         <v>373669</v>
       </c>
       <c r="C35" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E35" t="n">
         <v>69</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -615,10 +615,10 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D3" t="n">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E3" t="n">
         <v>110</v>
@@ -653,10 +653,10 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D5" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E5" t="n">
         <v>109</v>
@@ -672,10 +672,10 @@
         <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D6" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E6" t="n">
         <v>82</v>
@@ -710,10 +710,10 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E8" t="n">
         <v>51</v>
@@ -767,10 +767,10 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E11" t="n">
         <v>52</v>
@@ -881,10 +881,10 @@
         <v>373706</v>
       </c>
       <c r="C17" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D17" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E17" t="n">
         <v>42</v>
@@ -1121,39 +1121,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Nillum Bibi</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>373710</v>
+        <v>373652</v>
       </c>
       <c r="C30" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D30" t="n">
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nillum Bibi</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>373652</v>
+        <v>373710</v>
       </c>
       <c r="C31" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1863</v>
+        <v>1822</v>
       </c>
       <c r="C3" t="n">
-        <v>1844</v>
+        <v>1800</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>773</v>
+        <v>790</v>
       </c>
       <c r="C4" t="n">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="D4" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1480</v>
+        <v>1526</v>
       </c>
       <c r="C5" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="D5" t="n">
-        <v>1117</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1863</v>
+        <v>1822</v>
       </c>
       <c r="D2" t="n">
-        <v>1844</v>
+        <v>1800</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -653,10 +653,10 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D5" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E5" t="n">
         <v>109</v>
@@ -672,13 +672,13 @@
         <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="D6" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -691,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
         <v>230</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>373651</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E10" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -767,51 +767,51 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D11" t="n">
         <v>160</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373673</v>
+        <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="D12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373716</v>
+        <v>373673</v>
       </c>
       <c r="C13" t="n">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="D13" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E13" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -881,13 +881,13 @@
         <v>373706</v>
       </c>
       <c r="C17" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D17" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -1121,39 +1121,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nillum Bibi</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>373652</v>
+        <v>373710</v>
       </c>
       <c r="C30" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Nillum Bibi</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>373710</v>
+        <v>373652</v>
       </c>
       <c r="C31" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1223,13 +1223,13 @@
         <v>373669</v>
       </c>
       <c r="C35" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D35" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E35" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1526</v>
+        <v>1404</v>
       </c>
       <c r="C5" t="n">
-        <v>375</v>
+        <v>420</v>
       </c>
       <c r="D5" t="n">
-        <v>1151</v>
+        <v>984</v>
       </c>
     </row>
     <row r="6">
@@ -615,70 +615,70 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D3" t="n">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373684</v>
+        <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>293</v>
+        <v>341</v>
       </c>
       <c r="D4" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373648</v>
+        <v>373684</v>
       </c>
       <c r="C5" t="n">
-        <v>373</v>
+        <v>293</v>
       </c>
       <c r="D5" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E5" t="n">
-        <v>109</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373646</v>
+        <v>373648</v>
       </c>
       <c r="C6" t="n">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="D6" t="n">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E6" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
@@ -691,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="D7" t="n">
         <v>235</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="D8" t="n">
         <v>230</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>373651</v>
       </c>
       <c r="C10" t="n">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D10" t="n">
         <v>167</v>
       </c>
       <c r="E10" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">
@@ -767,13 +767,13 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D11" t="n">
         <v>160</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -786,13 +786,13 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D12" t="n">
         <v>145</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -824,13 +824,13 @@
         <v>373712</v>
       </c>
       <c r="C14" t="n">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D14" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E14" t="n">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15">
@@ -881,13 +881,13 @@
         <v>373706</v>
       </c>
       <c r="C17" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D17" t="n">
         <v>109</v>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -919,51 +919,51 @@
         <v>373692</v>
       </c>
       <c r="C19" t="n">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="D19" t="n">
         <v>102</v>
       </c>
       <c r="E19" t="n">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373699</v>
+        <v>373658</v>
       </c>
       <c r="C20" t="n">
-        <v>101</v>
+        <v>281</v>
       </c>
       <c r="D20" t="n">
         <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373658</v>
+        <v>373699</v>
       </c>
       <c r="C21" t="n">
-        <v>293</v>
+        <v>101</v>
       </c>
       <c r="D21" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>194</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1007,39 +1007,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>453925</v>
+        <v>373691</v>
       </c>
       <c r="C24" t="n">
-        <v>91</v>
+        <v>278</v>
       </c>
       <c r="D24" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>373691</v>
+        <v>453925</v>
       </c>
       <c r="C25" t="n">
-        <v>288</v>
+        <v>91</v>
       </c>
       <c r="D25" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E25" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1128,13 +1128,13 @@
         <v>373710</v>
       </c>
       <c r="C30" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D30" t="n">
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -1223,13 +1223,13 @@
         <v>373669</v>
       </c>
       <c r="C35" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D35" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E35" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1404</v>
+        <v>1392</v>
       </c>
       <c r="C5" t="n">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="D5" t="n">
         <v>984</v>
@@ -615,10 +615,10 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D3" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E3" t="n">
         <v>90</v>
@@ -634,10 +634,10 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D4" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E4" t="n">
         <v>74</v>
@@ -672,10 +672,10 @@
         <v>373648</v>
       </c>
       <c r="C6" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D6" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E6" t="n">
         <v>91</v>
@@ -779,39 +779,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373716</v>
+        <v>373673</v>
       </c>
       <c r="C12" t="n">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373673</v>
+        <v>373716</v>
       </c>
       <c r="C13" t="n">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="D13" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -881,10 +881,10 @@
         <v>373706</v>
       </c>
       <c r="C17" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D17" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E17" t="n">
         <v>35</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="C4" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D4" t="n">
         <v>338</v>
@@ -615,10 +615,10 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D3" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E3" t="n">
         <v>90</v>
@@ -710,10 +710,10 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D8" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E8" t="n">
         <v>42</v>
@@ -805,10 +805,10 @@
         <v>373716</v>
       </c>
       <c r="C13" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D13" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E13" t="n">
         <v>37</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1822</v>
+        <v>1744</v>
       </c>
       <c r="C3" t="n">
-        <v>1800</v>
+        <v>1721</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>786</v>
+        <v>805</v>
       </c>
       <c r="C4" t="n">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D4" t="n">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1392</v>
+        <v>1485</v>
       </c>
       <c r="C5" t="n">
-        <v>408</v>
+        <v>367</v>
       </c>
       <c r="D5" t="n">
-        <v>984</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1822</v>
+        <v>1744</v>
       </c>
       <c r="D2" t="n">
-        <v>1800</v>
+        <v>1721</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -615,32 +615,32 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="D3" t="n">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373646</v>
+        <v>373648</v>
       </c>
       <c r="C4" t="n">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="D4" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5">
@@ -665,20 +665,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373648</v>
+        <v>373646</v>
       </c>
       <c r="C6" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D6" t="n">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="E6" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7">
@@ -691,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D7" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
         <v>229</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>373651</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="D10" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E10" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -767,13 +767,13 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D11" t="n">
         <v>160</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
@@ -805,13 +805,13 @@
         <v>373716</v>
       </c>
       <c r="C13" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D13" t="n">
         <v>136</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -827,10 +827,10 @@
         <v>324</v>
       </c>
       <c r="D14" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E14" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15">
@@ -881,13 +881,13 @@
         <v>373706</v>
       </c>
       <c r="C17" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D17" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
@@ -912,20 +912,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>373692</v>
+        <v>373699</v>
       </c>
       <c r="C19" t="n">
-        <v>274</v>
+        <v>101</v>
       </c>
       <c r="D19" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>172</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -938,32 +938,32 @@
         <v>373658</v>
       </c>
       <c r="C20" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E20" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373699</v>
+        <v>373692</v>
       </c>
       <c r="C21" t="n">
-        <v>101</v>
+        <v>273</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22">
@@ -1007,39 +1007,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>373691</v>
+        <v>453925</v>
       </c>
       <c r="C24" t="n">
-        <v>278</v>
+        <v>92</v>
       </c>
       <c r="D24" t="n">
         <v>90</v>
       </c>
       <c r="E24" t="n">
-        <v>188</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>453925</v>
+        <v>373691</v>
       </c>
       <c r="C25" t="n">
-        <v>91</v>
+        <v>278</v>
       </c>
       <c r="D25" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26">
@@ -1128,13 +1128,13 @@
         <v>373710</v>
       </c>
       <c r="C30" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31">
@@ -1223,13 +1223,13 @@
         <v>373669</v>
       </c>
       <c r="C35" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D35" t="n">
         <v>47</v>
       </c>
       <c r="E35" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1822</v>
+        <v>1677</v>
       </c>
       <c r="C3" t="n">
-        <v>1800</v>
+        <v>1648</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>786</v>
+        <v>845</v>
       </c>
       <c r="C4" t="n">
-        <v>448</v>
+        <v>493</v>
       </c>
       <c r="D4" t="n">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1392</v>
+        <v>1485</v>
       </c>
       <c r="C5" t="n">
-        <v>408</v>
+        <v>454</v>
       </c>
       <c r="D5" t="n">
-        <v>984</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1822</v>
+        <v>1677</v>
       </c>
       <c r="D2" t="n">
-        <v>1800</v>
+        <v>1648</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -615,70 +615,70 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="D3" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373646</v>
+        <v>373648</v>
       </c>
       <c r="C4" t="n">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="D4" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373684</v>
+        <v>373646</v>
       </c>
       <c r="C5" t="n">
-        <v>293</v>
+        <v>347</v>
       </c>
       <c r="D5" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373648</v>
+        <v>373684</v>
       </c>
       <c r="C6" t="n">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="D6" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E6" t="n">
-        <v>91</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -691,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D7" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
         <v>229</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -741,77 +741,77 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373651</v>
+        <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E10" t="n">
-        <v>119</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373705</v>
+        <v>373651</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>317</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373673</v>
+        <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="D12" t="n">
         <v>140</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373716</v>
+        <v>373673</v>
       </c>
       <c r="C13" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="D13" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -836,58 +836,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373671</v>
+        <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Furqan Ullah Khan</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373683</v>
+        <v>373671</v>
       </c>
       <c r="C16" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D16" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Furqan Ullah Khan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373706</v>
+        <v>373683</v>
       </c>
       <c r="C17" t="n">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="D17" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -1045,96 +1045,96 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Irum ikram</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>541376</v>
+        <v>373710</v>
       </c>
       <c r="C26" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D26" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Irum ikram</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>373665</v>
+        <v>541376</v>
       </c>
       <c r="C27" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D27" t="n">
         <v>83</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Naureen</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>884887</v>
+        <v>373665</v>
       </c>
       <c r="C28" t="n">
         <v>86</v>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jaweria</t>
+          <t>Naureen</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>163495</v>
+        <v>884887</v>
       </c>
       <c r="C29" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D29" t="n">
         <v>82</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Jaweria</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>373710</v>
+        <v>163495</v>
       </c>
       <c r="C30" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1159,77 +1159,77 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Anum Gul</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>373656</v>
+        <v>373669</v>
       </c>
       <c r="C32" t="n">
+        <v>131</v>
+      </c>
+      <c r="D32" t="n">
         <v>55</v>
       </c>
-      <c r="D32" t="n">
-        <v>51</v>
-      </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Muniba Shamim</t>
+          <t>Anum Gul</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>373659</v>
+        <v>373656</v>
       </c>
       <c r="C33" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D33" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nazia</t>
+          <t>Muniba Shamim</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>373657</v>
+        <v>373659</v>
       </c>
       <c r="C34" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D34" t="n">
         <v>49</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Nazia</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>373669</v>
+        <v>373657</v>
       </c>
       <c r="C35" t="n">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E35" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1539,30 +1539,30 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Aisha Aman</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>373704</v>
+        <v>752327</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
         <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Rahila Naaz</t>
+          <t>Aisha Aman</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>373715</v>
+        <v>373704</v>
       </c>
       <c r="C53" t="n">
         <v>3</v>
@@ -1577,11 +1577,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Robina Shaheen</t>
+          <t>Rahila Naaz</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>373639</v>
+        <v>373715</v>
       </c>
       <c r="C54" t="n">
         <v>3</v>
@@ -1596,68 +1596,68 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Iqra Bibi</t>
+          <t>Robina Shaheen</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>373708</v>
+        <v>373639</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
         <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mahnoorr</t>
+          <t>Iqra Bibi</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>373670</v>
+        <v>373708</v>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gul Rukh</t>
+          <t>Mahnoorr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>373644</v>
+        <v>373670</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Hijab Zahra</t>
+          <t>Gul Rukh</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>373637</v>
+        <v>373644</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -1672,11 +1672,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sidra Khan</t>
+          <t>Hijab Zahra</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>373645</v>
+        <v>373637</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -1685,6 +1685,25 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sidra Khan</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>373645</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1485</v>
+        <v>1428</v>
       </c>
       <c r="C5" t="n">
         <v>454</v>
       </c>
       <c r="D5" t="n">
-        <v>1031</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D3" t="n">
         <v>370</v>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
@@ -634,13 +634,13 @@
         <v>373648</v>
       </c>
       <c r="C4" t="n">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D4" t="n">
         <v>268</v>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
@@ -691,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D7" t="n">
         <v>237</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
         <v>229</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
         <v>179</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -767,13 +767,13 @@
         <v>373651</v>
       </c>
       <c r="C11" t="n">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D11" t="n">
         <v>178</v>
       </c>
       <c r="E11" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -786,13 +786,13 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D12" t="n">
         <v>140</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -824,13 +824,13 @@
         <v>373712</v>
       </c>
       <c r="C14" t="n">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D14" t="n">
         <v>130</v>
       </c>
       <c r="E14" t="n">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
@@ -843,13 +843,13 @@
         <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
@@ -919,13 +919,13 @@
         <v>373692</v>
       </c>
       <c r="C19" t="n">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D19" t="n">
         <v>102</v>
       </c>
       <c r="E19" t="n">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20">
@@ -938,13 +938,13 @@
         <v>373658</v>
       </c>
       <c r="C20" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D20" t="n">
         <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21">
@@ -1014,13 +1014,13 @@
         <v>373691</v>
       </c>
       <c r="C24" t="n">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D24" t="n">
         <v>90</v>
       </c>
       <c r="E24" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25">
@@ -1052,13 +1052,13 @@
         <v>373710</v>
       </c>
       <c r="C26" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D26" t="n">
         <v>84</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
@@ -1166,13 +1166,13 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D32" t="n">
         <v>55</v>
       </c>
       <c r="E32" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1677</v>
+        <v>1639</v>
       </c>
       <c r="C3" t="n">
-        <v>1648</v>
+        <v>1609</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>845</v>
+        <v>869</v>
       </c>
       <c r="C4" t="n">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="D4" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1428</v>
+        <v>1453</v>
       </c>
       <c r="C5" t="n">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D5" t="n">
-        <v>974</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1677</v>
+        <v>1639</v>
       </c>
       <c r="D2" t="n">
-        <v>1648</v>
+        <v>1609</v>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -615,51 +615,51 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D3" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373648</v>
+        <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D4" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373646</v>
+        <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="D5" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
@@ -691,10 +691,10 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D7" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E7" t="n">
         <v>80</v>
@@ -710,70 +710,70 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D8" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373649</v>
+        <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>192</v>
+        <v>320</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373705</v>
+        <v>373649</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373651</v>
+        <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>309</v>
+        <v>232</v>
       </c>
       <c r="D11" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E11" t="n">
-        <v>131</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -786,13 +786,13 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -824,51 +824,51 @@
         <v>373712</v>
       </c>
       <c r="C14" t="n">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D14" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E14" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373706</v>
+        <v>373671</v>
       </c>
       <c r="C15" t="n">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373671</v>
+        <v>373706</v>
       </c>
       <c r="C16" t="n">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="D16" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -941,10 +941,10 @@
         <v>278</v>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E20" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21">
@@ -1007,96 +1007,96 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>373691</v>
+        <v>453925</v>
       </c>
       <c r="C24" t="n">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="D24" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" t="n">
-        <v>183</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>453925</v>
+        <v>373691</v>
       </c>
       <c r="C25" t="n">
-        <v>91</v>
+        <v>267</v>
       </c>
       <c r="D25" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Irum ikram</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>373710</v>
+        <v>541376</v>
       </c>
       <c r="C26" t="n">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="D26" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irum ikram</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>541376</v>
+        <v>373665</v>
       </c>
       <c r="C27" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D27" t="n">
         <v>83</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>373665</v>
+        <v>373710</v>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="D28" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
@@ -1166,10 +1166,10 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D32" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E32" t="n">
         <v>74</v>
@@ -1425,30 +1425,30 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sadia rustum</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>852541</v>
+        <v>752327</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Usman Ali</t>
+          <t>Sadia rustum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>373687</v>
+        <v>852541</v>
       </c>
       <c r="C47" t="n">
         <v>5</v>
@@ -1463,49 +1463,49 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Muhammad Noor</t>
+          <t>Usman Ali</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>373701</v>
+        <v>373687</v>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Muhammad Naeem</t>
+          <t>Muhammad Noor</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>373694</v>
+        <v>373701</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Muhammad Shahid Khan</t>
+          <t>Muhammad Naeem</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>373662</v>
+        <v>373694</v>
       </c>
       <c r="C50" t="n">
         <v>3</v>
@@ -1520,11 +1520,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sajjad Khan</t>
+          <t>Muhammad Shahid Khan</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>373700</v>
+        <v>373662</v>
       </c>
       <c r="C51" t="n">
         <v>3</v>
@@ -1539,20 +1539,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Sajjad Khan</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>752327</v>
+        <v>373700</v>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1453</v>
+        <v>1426</v>
       </c>
       <c r="C5" t="n">
         <v>451</v>
       </c>
       <c r="D5" t="n">
-        <v>1002</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D3" t="n">
         <v>372</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
@@ -634,13 +634,13 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D4" t="n">
         <v>274</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D5" t="n">
         <v>270</v>
       </c>
       <c r="E5" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
@@ -729,13 +729,13 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
         <v>183</v>
       </c>
       <c r="E9" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -767,13 +767,13 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D11" t="n">
         <v>180</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
@@ -786,13 +786,13 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D12" t="n">
         <v>145</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -824,13 +824,13 @@
         <v>373712</v>
       </c>
       <c r="C14" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D14" t="n">
         <v>126</v>
       </c>
       <c r="E14" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15">
@@ -862,13 +862,13 @@
         <v>373706</v>
       </c>
       <c r="C16" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D16" t="n">
         <v>121</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
@@ -1033,13 +1033,13 @@
         <v>373691</v>
       </c>
       <c r="C25" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D25" t="n">
         <v>84</v>
       </c>
       <c r="E25" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26">
@@ -1166,13 +1166,13 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D32" t="n">
         <v>51</v>
       </c>
       <c r="E32" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
@@ -1432,13 +1432,13 @@
         <v>752327</v>
       </c>
       <c r="C46" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D46" t="n">
         <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>869</v>
+        <v>850</v>
       </c>
       <c r="C4" t="n">
         <v>509</v>
       </c>
       <c r="D4" t="n">
-        <v>360</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D5" t="n">
         <v>270</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -729,13 +729,13 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
         <v>183</v>
       </c>
       <c r="E9" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -1166,13 +1166,13 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D32" t="n">
         <v>51</v>
       </c>
       <c r="E32" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1639</v>
+        <v>1601</v>
       </c>
       <c r="C3" t="n">
-        <v>1609</v>
+        <v>1570</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>850</v>
+        <v>868</v>
       </c>
       <c r="C4" t="n">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="D4" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1426</v>
+        <v>1444</v>
       </c>
       <c r="C5" t="n">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="D5" t="n">
-        <v>975</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1639</v>
+        <v>1601</v>
       </c>
       <c r="D2" t="n">
-        <v>1609</v>
+        <v>1570</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -615,10 +615,10 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D3" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E3" t="n">
         <v>91</v>
@@ -634,13 +634,13 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D4" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D8" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -729,13 +729,13 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="E9" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -767,13 +767,13 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D11" t="n">
         <v>180</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -836,39 +836,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373671</v>
+        <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373706</v>
+        <v>373671</v>
       </c>
       <c r="C16" t="n">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="D16" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1166,13 +1166,13 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D32" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E32" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
@@ -1349,36 +1349,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lati khan</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>652938</v>
+        <v>752327</v>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D42" t="n">
         <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Saba Ramzan</t>
+          <t>Lati khan</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>373703</v>
+        <v>652938</v>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -1387,11 +1387,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Shehla Noor</t>
+          <t>Saba Ramzan</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>373650</v>
+        <v>373703</v>
       </c>
       <c r="C44" t="n">
         <v>9</v>
@@ -1406,39 +1406,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Muhammad naeem</t>
+          <t>Shehla Noor</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>571571</v>
+        <v>373650</v>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Muhammad naeem</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>752327</v>
+        <v>571571</v>
       </c>
       <c r="C46" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C4" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D4" t="n">
         <v>346</v>
@@ -634,10 +634,10 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D4" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E4" t="n">
         <v>85</v>
@@ -653,10 +653,10 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D5" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E5" t="n">
         <v>84</v>
@@ -767,10 +767,10 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D11" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E11" t="n">
         <v>52</v>
@@ -786,10 +786,10 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D12" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E12" t="n">
         <v>39</v>
@@ -919,10 +919,10 @@
         <v>373692</v>
       </c>
       <c r="C19" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D19" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E19" t="n">
         <v>165</v>
@@ -931,39 +931,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373658</v>
+        <v>373699</v>
       </c>
       <c r="C20" t="n">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="D20" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>177</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373699</v>
+        <v>373658</v>
       </c>
       <c r="C21" t="n">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1601</v>
+        <v>1586</v>
       </c>
       <c r="C3" t="n">
-        <v>1570</v>
+        <v>1551</v>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="C4" t="n">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="D4" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1444</v>
+        <v>1471</v>
       </c>
       <c r="C5" t="n">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="D5" t="n">
-        <v>983</v>
+        <v>997</v>
       </c>
     </row>
     <row r="6">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1601</v>
+        <v>1586</v>
       </c>
       <c r="D2" t="n">
-        <v>1570</v>
+        <v>1551</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -615,10 +615,10 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D3" t="n">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E3" t="n">
         <v>91</v>
@@ -634,13 +634,13 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="D4" t="n">
         <v>280</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
@@ -653,10 +653,10 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D5" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E5" t="n">
         <v>84</v>
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D8" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
@@ -729,51 +729,51 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E9" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373649</v>
+        <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373705</v>
+        <v>373649</v>
       </c>
       <c r="C11" t="n">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -786,13 +786,13 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -843,10 +843,10 @@
         <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E15" t="n">
         <v>40</v>
@@ -1045,58 +1045,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Irum ikram</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>541376</v>
+        <v>373710</v>
       </c>
       <c r="C26" t="n">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D26" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Irum ikram</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>373665</v>
+        <v>541376</v>
       </c>
       <c r="C27" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D27" t="n">
         <v>83</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>373710</v>
+        <v>373665</v>
       </c>
       <c r="C28" t="n">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E28" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1166,10 +1166,10 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D32" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E32" t="n">
         <v>57</v>
@@ -1330,39 +1330,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Zain Ul Abideen</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>373667</v>
+        <v>752327</v>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D41" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Zain Ul Abideen</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>752327</v>
+        <v>373667</v>
       </c>
       <c r="C42" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1586</v>
+        <v>1558</v>
       </c>
       <c r="C3" t="n">
-        <v>1551</v>
+        <v>1520</v>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="C4" t="n">
-        <v>537</v>
+        <v>553</v>
       </c>
       <c r="D4" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1471</v>
+        <v>1519</v>
       </c>
       <c r="C5" t="n">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="D5" t="n">
-        <v>997</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1586</v>
+        <v>1558</v>
       </c>
       <c r="D2" t="n">
-        <v>1551</v>
+        <v>1520</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="D3" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
@@ -634,13 +634,13 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D4" t="n">
         <v>280</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="D5" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D8" t="n">
         <v>234</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -729,13 +729,13 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D9" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
@@ -748,13 +748,13 @@
         <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -786,13 +786,13 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D12" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -1026,39 +1026,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>373691</v>
+        <v>373710</v>
       </c>
       <c r="C25" t="n">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="D25" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E25" t="n">
-        <v>181</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>373710</v>
+        <v>373691</v>
       </c>
       <c r="C26" t="n">
-        <v>113</v>
+        <v>265</v>
       </c>
       <c r="D26" t="n">
         <v>84</v>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27">
@@ -1292,58 +1292,58 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Laiba Khan</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>373653</v>
+        <v>752327</v>
       </c>
       <c r="C39" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D39" t="n">
         <v>22</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Chashm Gul</t>
+          <t>Laiba Khan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>373695</v>
+        <v>373653</v>
       </c>
       <c r="C40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D40" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E40" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Chashm Gul</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>752327</v>
+        <v>373695</v>
       </c>
       <c r="C41" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E41" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1558</v>
+        <v>1544</v>
       </c>
       <c r="C3" t="n">
-        <v>1520</v>
+        <v>1506</v>
       </c>
       <c r="D3" t="n">
         <v>38</v>
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>904</v>
+        <v>927</v>
       </c>
       <c r="C4" t="n">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="D4" t="n">
-        <v>351</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1519</v>
+        <v>1596</v>
       </c>
       <c r="C5" t="n">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="D5" t="n">
-        <v>1031</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -596,10 +596,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1558</v>
+        <v>1544</v>
       </c>
       <c r="D2" t="n">
-        <v>1520</v>
+        <v>1506</v>
       </c>
       <c r="E2" t="n">
         <v>38</v>
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="D3" t="n">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E3" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
@@ -634,13 +634,13 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="D4" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D5" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -691,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D7" t="n">
         <v>238</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -729,13 +729,13 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="E9" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
@@ -748,13 +748,13 @@
         <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -786,13 +786,13 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D12" t="n">
         <v>149</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -843,13 +843,13 @@
         <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D15" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
@@ -912,58 +912,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>373692</v>
+        <v>373699</v>
       </c>
       <c r="C19" t="n">
-        <v>266</v>
+        <v>101</v>
       </c>
       <c r="D19" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373699</v>
+        <v>373658</v>
       </c>
       <c r="C20" t="n">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373658</v>
+        <v>373692</v>
       </c>
       <c r="C21" t="n">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="D21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E21" t="n">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22">
@@ -1033,13 +1033,13 @@
         <v>373710</v>
       </c>
       <c r="C25" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D25" t="n">
         <v>85</v>
       </c>
       <c r="E25" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
@@ -1166,13 +1166,13 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D32" t="n">
         <v>55</v>
       </c>
       <c r="E32" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
@@ -1273,39 +1273,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Munawar Khan</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>373668</v>
+        <v>752327</v>
       </c>
       <c r="C38" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D38" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Munawar Khan</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>752327</v>
+        <v>373668</v>
       </c>
       <c r="C39" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D39" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E39" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1544</v>
+        <v>1534</v>
       </c>
       <c r="C3" t="n">
-        <v>1506</v>
+        <v>1496</v>
       </c>
       <c r="D3" t="n">
         <v>38</v>
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="C4" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D4" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="C5" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D5" t="n">
-        <v>1093</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="6">
@@ -525,10 +525,10 @@
         <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -596,10 +596,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1544</v>
+        <v>1534</v>
       </c>
       <c r="D2" t="n">
-        <v>1506</v>
+        <v>1496</v>
       </c>
       <c r="E2" t="n">
         <v>38</v>
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -817,39 +817,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373712</v>
+        <v>373706</v>
       </c>
       <c r="C14" t="n">
-        <v>308</v>
+        <v>172</v>
       </c>
       <c r="D14" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E14" t="n">
-        <v>182</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373706</v>
+        <v>373712</v>
       </c>
       <c r="C15" t="n">
-        <v>170</v>
+        <v>308</v>
       </c>
       <c r="D15" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E15" t="n">
-        <v>45</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16">
@@ -1166,13 +1166,13 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D32" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E32" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1534</v>
+        <v>1526</v>
       </c>
       <c r="C3" t="n">
-        <v>1496</v>
+        <v>1487</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C4" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D4" t="n">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1603</v>
+        <v>1556</v>
       </c>
       <c r="C5" t="n">
         <v>505</v>
       </c>
       <c r="D5" t="n">
-        <v>1098</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="6">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1534</v>
+        <v>1526</v>
       </c>
       <c r="D2" t="n">
-        <v>1496</v>
+        <v>1487</v>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="D3" t="n">
         <v>395</v>
       </c>
       <c r="E3" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -634,13 +634,13 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D4" t="n">
         <v>284</v>
       </c>
       <c r="E4" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D5" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E5" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -691,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D7" t="n">
         <v>238</v>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -710,13 +710,13 @@
         <v>373642</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
         <v>238</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
@@ -729,13 +729,13 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D9" t="n">
         <v>208</v>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
@@ -748,13 +748,13 @@
         <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
@@ -786,13 +786,13 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D12" t="n">
         <v>149</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -817,39 +817,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373706</v>
+        <v>373712</v>
       </c>
       <c r="C14" t="n">
-        <v>172</v>
+        <v>308</v>
       </c>
       <c r="D14" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373712</v>
+        <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="D15" t="n">
         <v>126</v>
       </c>
       <c r="E15" t="n">
-        <v>182</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -912,58 +912,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>373699</v>
+        <v>373692</v>
       </c>
       <c r="C19" t="n">
+        <v>266</v>
+      </c>
+      <c r="D19" t="n">
         <v>101</v>
       </c>
-      <c r="D19" t="n">
-        <v>100</v>
-      </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373658</v>
+        <v>373699</v>
       </c>
       <c r="C20" t="n">
-        <v>276</v>
+        <v>101</v>
       </c>
       <c r="D20" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>177</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373692</v>
+        <v>373658</v>
       </c>
       <c r="C21" t="n">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="D21" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E21" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22">
@@ -1033,13 +1033,13 @@
         <v>373710</v>
       </c>
       <c r="C25" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D25" t="n">
         <v>85</v>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
@@ -1166,13 +1166,13 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D32" t="n">
         <v>57</v>
       </c>
       <c r="E32" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
@@ -1280,13 +1280,13 @@
         <v>752327</v>
       </c>
       <c r="C38" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D38" t="n">
         <v>33</v>
       </c>
       <c r="E38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>933</v>
+        <v>913</v>
       </c>
       <c r="C4" t="n">
-        <v>573</v>
+        <v>553</v>
       </c>
       <c r="D4" t="n">
         <v>360</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1556</v>
+        <v>1532</v>
       </c>
       <c r="C5" t="n">
-        <v>505</v>
+        <v>481</v>
       </c>
       <c r="D5" t="n">
         <v>1051</v>
@@ -634,10 +634,10 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D4" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E4" t="n">
         <v>107</v>
@@ -684,39 +684,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373696</v>
+        <v>373642</v>
       </c>
       <c r="C7" t="n">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="D7" t="n">
         <v>238</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373642</v>
+        <v>373696</v>
       </c>
       <c r="C8" t="n">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="D8" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E8" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -729,10 +729,10 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D9" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E9" t="n">
         <v>142</v>
@@ -741,39 +741,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373705</v>
+        <v>373649</v>
       </c>
       <c r="C10" t="n">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373649</v>
+        <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="D11" t="n">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -786,10 +786,10 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E12" t="n">
         <v>48</v>
@@ -836,39 +836,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373706</v>
+        <v>373671</v>
       </c>
       <c r="C15" t="n">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="D15" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373671</v>
+        <v>373706</v>
       </c>
       <c r="C16" t="n">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="D16" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
@@ -919,10 +919,10 @@
         <v>373692</v>
       </c>
       <c r="C19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D19" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
         <v>165</v>
@@ -957,10 +957,10 @@
         <v>373658</v>
       </c>
       <c r="C21" t="n">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E21" t="n">
         <v>177</v>
@@ -1026,77 +1026,77 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>373710</v>
+        <v>373691</v>
       </c>
       <c r="C25" t="n">
-        <v>114</v>
+        <v>265</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E25" t="n">
-        <v>29</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Irum ikram</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>373691</v>
+        <v>541376</v>
       </c>
       <c r="C26" t="n">
-        <v>265</v>
+        <v>88</v>
       </c>
       <c r="D26" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26" t="n">
-        <v>181</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irum ikram</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>541376</v>
+        <v>373665</v>
       </c>
       <c r="C27" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D27" t="n">
         <v>83</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>373665</v>
+        <v>373710</v>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="D28" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
@@ -1159,39 +1159,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Anum Gul</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>373669</v>
+        <v>373656</v>
       </c>
       <c r="C32" t="n">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D32" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E32" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Anum Gul</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>373656</v>
+        <v>373669</v>
       </c>
       <c r="C33" t="n">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1526</v>
+        <v>1441</v>
       </c>
       <c r="C3" t="n">
-        <v>1487</v>
+        <v>1400</v>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>913</v>
+        <v>957</v>
       </c>
       <c r="C4" t="n">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="D4" t="n">
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1532</v>
+        <v>1605</v>
       </c>
       <c r="C5" t="n">
-        <v>481</v>
+        <v>508</v>
       </c>
       <c r="D5" t="n">
-        <v>1051</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1526</v>
+        <v>1441</v>
       </c>
       <c r="D2" t="n">
-        <v>1487</v>
+        <v>1400</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="D3" t="n">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
@@ -634,13 +634,13 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="D4" t="n">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E4" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6">
@@ -691,13 +691,13 @@
         <v>373642</v>
       </c>
       <c r="C7" t="n">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D7" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -729,13 +729,13 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="D9" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="E9" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -767,13 +767,13 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
@@ -786,13 +786,13 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -836,39 +836,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373671</v>
+        <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373706</v>
+        <v>373671</v>
       </c>
       <c r="C16" t="n">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="D16" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1090,13 +1090,13 @@
         <v>373710</v>
       </c>
       <c r="C28" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D28" t="n">
         <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
@@ -1235,58 +1235,58 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alia Khan</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>373681</v>
+        <v>752327</v>
       </c>
       <c r="C36" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="D36" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lati khan</t>
+          <t>Alia Khan</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>671211</v>
+        <v>373681</v>
       </c>
       <c r="C37" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D37" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Lati khan</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>752327</v>
+        <v>671211</v>
       </c>
       <c r="C38" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D38" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E38" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1441</v>
+        <v>1403</v>
       </c>
       <c r="C3" t="n">
-        <v>1400</v>
+        <v>1358</v>
       </c>
       <c r="D3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>957</v>
+        <v>984</v>
       </c>
       <c r="C4" t="n">
-        <v>585</v>
+        <v>607</v>
       </c>
       <c r="D4" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1605</v>
+        <v>1639</v>
       </c>
       <c r="C5" t="n">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="D5" t="n">
-        <v>1097</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="6">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1441</v>
+        <v>1403</v>
       </c>
       <c r="D2" t="n">
-        <v>1400</v>
+        <v>1358</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -615,10 +615,10 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D3" t="n">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E3" t="n">
         <v>107</v>
@@ -634,13 +634,13 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D4" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E4" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D5" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -691,13 +691,13 @@
         <v>373642</v>
       </c>
       <c r="C7" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D7" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -729,13 +729,13 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="D9" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="E9" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
@@ -767,13 +767,13 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D11" t="n">
         <v>171</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -786,13 +786,13 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D12" t="n">
         <v>150</v>
       </c>
       <c r="E12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -843,13 +843,13 @@
         <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D15" t="n">
         <v>123</v>
       </c>
       <c r="E15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -1090,13 +1090,13 @@
         <v>373710</v>
       </c>
       <c r="C28" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D28" t="n">
         <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
@@ -1159,96 +1159,96 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Anum Gul</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>373656</v>
+        <v>752327</v>
       </c>
       <c r="C32" t="n">
+        <v>94</v>
+      </c>
+      <c r="D32" t="n">
         <v>55</v>
       </c>
-      <c r="D32" t="n">
-        <v>51</v>
-      </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Anum Gul</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>373669</v>
+        <v>373656</v>
       </c>
       <c r="C33" t="n">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E33" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Muniba Shamim</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>373659</v>
+        <v>373669</v>
       </c>
       <c r="C34" t="n">
+        <v>108</v>
+      </c>
+      <c r="D34" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" t="n">
         <v>58</v>
-      </c>
-      <c r="D34" t="n">
-        <v>49</v>
-      </c>
-      <c r="E34" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nazia</t>
+          <t>Muniba Shamim</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>373657</v>
+        <v>373659</v>
       </c>
       <c r="C35" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D35" t="n">
         <v>49</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Nazia</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>752327</v>
+        <v>373657</v>
       </c>
       <c r="C36" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D36" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E36" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1403</v>
+        <v>1334</v>
       </c>
       <c r="C3" t="n">
-        <v>1358</v>
+        <v>1285</v>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>984</v>
+        <v>1021</v>
       </c>
       <c r="C4" t="n">
-        <v>607</v>
+        <v>632</v>
       </c>
       <c r="D4" t="n">
-        <v>377</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1639</v>
+        <v>1688</v>
       </c>
       <c r="C5" t="n">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="D5" t="n">
-        <v>1116</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1403</v>
+        <v>1334</v>
       </c>
       <c r="D2" t="n">
-        <v>1358</v>
+        <v>1285</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="D3" t="n">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4">
@@ -634,13 +634,13 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="D4" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E4" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="D5" t="n">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="E5" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -691,13 +691,13 @@
         <v>373642</v>
       </c>
       <c r="C7" t="n">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -729,13 +729,13 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="D9" t="n">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E9" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
@@ -767,13 +767,13 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D11" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -817,39 +817,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373712</v>
+        <v>373706</v>
       </c>
       <c r="C14" t="n">
-        <v>308</v>
+        <v>177</v>
       </c>
       <c r="D14" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E14" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373706</v>
+        <v>373712</v>
       </c>
       <c r="C15" t="n">
-        <v>170</v>
+        <v>308</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16">
@@ -1026,77 +1026,77 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>373691</v>
+        <v>373710</v>
       </c>
       <c r="C25" t="n">
-        <v>265</v>
+        <v>122</v>
       </c>
       <c r="D25" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E25" t="n">
-        <v>181</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Irum ikram</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>541376</v>
+        <v>373691</v>
       </c>
       <c r="C26" t="n">
-        <v>88</v>
+        <v>265</v>
       </c>
       <c r="D26" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Irum ikram</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>373665</v>
+        <v>541376</v>
       </c>
       <c r="C27" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D27" t="n">
         <v>83</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>373710</v>
+        <v>373665</v>
       </c>
       <c r="C28" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E28" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1140,39 +1140,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nillum Bibi</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>373652</v>
+        <v>752327</v>
       </c>
       <c r="C31" t="n">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="D31" t="n">
         <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Nillum Bibi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>752327</v>
+        <v>373652</v>
       </c>
       <c r="C32" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1334</v>
+        <v>1310</v>
       </c>
       <c r="C3" t="n">
-        <v>1285</v>
+        <v>1259</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1021</v>
+        <v>1048</v>
       </c>
       <c r="C4" t="n">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="D4" t="n">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1688</v>
+        <v>1722</v>
       </c>
       <c r="C5" t="n">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="D5" t="n">
-        <v>1135</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1334</v>
+        <v>1310</v>
       </c>
       <c r="D2" t="n">
-        <v>1285</v>
+        <v>1259</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="D3" t="n">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
@@ -634,13 +634,13 @@
         <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="D4" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E4" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D5" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
@@ -691,13 +691,13 @@
         <v>373642</v>
       </c>
       <c r="C7" t="n">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
         <v>247</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -767,10 +767,10 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D11" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E11" t="n">
         <v>74</v>
@@ -824,13 +824,13 @@
         <v>373706</v>
       </c>
       <c r="C14" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D14" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -1033,13 +1033,13 @@
         <v>373710</v>
       </c>
       <c r="C25" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D25" t="n">
         <v>87</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
@@ -1147,13 +1147,13 @@
         <v>752327</v>
       </c>
       <c r="C31" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
@@ -1444,17 +1444,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sadia rustum</t>
+          <t>Summiya Hayat 123</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>852541</v>
+        <v>51020</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1463,11 +1463,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Usman Ali</t>
+          <t>Sadia rustum</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>373687</v>
+        <v>852541</v>
       </c>
       <c r="C48" t="n">
         <v>5</v>
@@ -1482,49 +1482,49 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Muhammad Noor</t>
+          <t>Usman Ali</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>373701</v>
+        <v>373687</v>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Muhammad Naeem</t>
+          <t>Muhammad Noor</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>373694</v>
+        <v>373701</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Muhammad Shahid Khan</t>
+          <t>Muhammad Naeem</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>373662</v>
+        <v>373694</v>
       </c>
       <c r="C51" t="n">
         <v>3</v>
@@ -1539,11 +1539,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sajjad Khan</t>
+          <t>Muhammad Shahid Khan</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>373700</v>
+        <v>373662</v>
       </c>
       <c r="C52" t="n">
         <v>3</v>
@@ -1558,30 +1558,30 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Aisha Aman</t>
+          <t>Sajjad Khan</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>373704</v>
+        <v>373700</v>
       </c>
       <c r="C53" t="n">
         <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Rahila Naaz</t>
+          <t>Aisha Aman</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>373715</v>
+        <v>373704</v>
       </c>
       <c r="C54" t="n">
         <v>3</v>
@@ -1596,11 +1596,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Robina Shaheen</t>
+          <t>Rahila Naaz</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>373639</v>
+        <v>373715</v>
       </c>
       <c r="C55" t="n">
         <v>3</v>
@@ -1615,68 +1615,68 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Iqra Bibi</t>
+          <t>Robina Shaheen</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>373708</v>
+        <v>373639</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mahnoorr</t>
+          <t>Iqra Bibi</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>373670</v>
+        <v>373708</v>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Gul Rukh</t>
+          <t>Mahnoorr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>373644</v>
+        <v>373670</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Hijab Zahra</t>
+          <t>Gul Rukh</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>373637</v>
+        <v>373644</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -1691,11 +1691,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sidra Khan</t>
+          <t>Hijab Zahra</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>373645</v>
+        <v>373637</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -1704,6 +1704,25 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sidra Khan</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>373645</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1048</v>
+        <v>1029</v>
       </c>
       <c r="C4" t="n">
-        <v>652</v>
+        <v>875</v>
       </c>
       <c r="D4" t="n">
-        <v>396</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1722</v>
+        <v>1701</v>
       </c>
       <c r="C5" t="n">
-        <v>573</v>
+        <v>833</v>
       </c>
       <c r="D5" t="n">
-        <v>1149</v>
+        <v>868</v>
       </c>
     </row>
     <row r="6">
@@ -615,108 +615,108 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D3" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E3" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373646</v>
+        <v>373648</v>
       </c>
       <c r="C4" t="n">
-        <v>449</v>
+        <v>402</v>
       </c>
       <c r="D4" t="n">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c r="E4" t="n">
-        <v>143</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373648</v>
+        <v>373646</v>
       </c>
       <c r="C5" t="n">
-        <v>402</v>
+        <v>449</v>
       </c>
       <c r="D5" t="n">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="E5" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Irum Ikram</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>373684</v>
+        <v>373642</v>
       </c>
       <c r="C6" t="n">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="D6" t="n">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Irum Ikram</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373642</v>
+        <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="D7" t="n">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373696</v>
+        <v>373684</v>
       </c>
       <c r="C8" t="n">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="D8" t="n">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -732,29 +732,29 @@
         <v>386</v>
       </c>
       <c r="D9" t="n">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="E9" t="n">
-        <v>154</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373649</v>
+        <v>373712</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -767,298 +767,298 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D11" t="n">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373716</v>
+        <v>373649</v>
       </c>
       <c r="C12" t="n">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D12" t="n">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373673</v>
+        <v>373658</v>
       </c>
       <c r="C13" t="n">
-        <v>140</v>
+        <v>274</v>
       </c>
       <c r="D13" t="n">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Laiba Shams</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373706</v>
+        <v>373716</v>
       </c>
       <c r="C14" t="n">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="D14" t="n">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Laiba Shams</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>373712</v>
+        <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>308</v>
+        <v>174</v>
       </c>
       <c r="D15" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E15" t="n">
-        <v>182</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bushra Ayub</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373671</v>
+        <v>373673</v>
       </c>
       <c r="C16" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D16" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Furqan Ullah Khan</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373683</v>
+        <v>373691</v>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>265</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Asma Gull</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>373672</v>
+        <v>373692</v>
       </c>
       <c r="C18" t="n">
-        <v>109</v>
+        <v>257</v>
       </c>
       <c r="D18" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Bushra Ayub</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>373692</v>
+        <v>373671</v>
       </c>
       <c r="C19" t="n">
-        <v>265</v>
+        <v>126</v>
       </c>
       <c r="D19" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E19" t="n">
-        <v>165</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Furqan Ullah Khan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>373699</v>
+        <v>373683</v>
       </c>
       <c r="C20" t="n">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Asma Gull</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373658</v>
+        <v>373672</v>
       </c>
       <c r="C21" t="n">
-        <v>274</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E21" t="n">
-        <v>177</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Muhammad Yousaf</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>373690</v>
+        <v>373699</v>
       </c>
       <c r="C22" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D22" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Muhammad Yousaf</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>564273</v>
+        <v>373690</v>
       </c>
       <c r="C23" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D23" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>453925</v>
+        <v>564273</v>
       </c>
       <c r="C24" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D24" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>373710</v>
+        <v>453925</v>
       </c>
       <c r="C25" t="n">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="D25" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>373691</v>
+        <v>373710</v>
       </c>
       <c r="C26" t="n">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="D26" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E26" t="n">
-        <v>181</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -1140,77 +1140,77 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>752327</v>
+        <v>373669</v>
       </c>
       <c r="C31" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E31" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nillum Bibi</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>373652</v>
+        <v>752327</v>
       </c>
       <c r="C32" t="n">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Anum Gul</t>
+          <t>Nillum Bibi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>373656</v>
+        <v>373652</v>
       </c>
       <c r="C33" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D33" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>Anum Gul</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>373669</v>
+        <v>373656</v>
       </c>
       <c r="C34" t="n">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E34" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1444,17 +1444,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Summiya Hayat 123</t>
+          <t>Sadia rustum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>51020</v>
+        <v>852541</v>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1463,11 +1463,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sadia rustum</t>
+          <t>Usman Ali</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>852541</v>
+        <v>373687</v>
       </c>
       <c r="C48" t="n">
         <v>5</v>
@@ -1482,49 +1482,49 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Usman Ali</t>
+          <t>Muhammad Noor</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>373687</v>
+        <v>373701</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Muhammad Noor</t>
+          <t>Muhammad Naeem</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>373701</v>
+        <v>373694</v>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Muhammad Naeem</t>
+          <t>Muhammad Shahid Khan</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>373694</v>
+        <v>373662</v>
       </c>
       <c r="C51" t="n">
         <v>3</v>
@@ -1539,11 +1539,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Muhammad Shahid Khan</t>
+          <t>Sajjad Khan</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>373662</v>
+        <v>373700</v>
       </c>
       <c r="C52" t="n">
         <v>3</v>
@@ -1558,30 +1558,30 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sajjad Khan</t>
+          <t>Aisha Aman</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>373700</v>
+        <v>373704</v>
       </c>
       <c r="C53" t="n">
         <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Aisha Aman</t>
+          <t>Rahila Naaz</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>373704</v>
+        <v>373715</v>
       </c>
       <c r="C54" t="n">
         <v>3</v>
@@ -1596,11 +1596,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Rahila Naaz</t>
+          <t>Robina Shaheen</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>373715</v>
+        <v>373639</v>
       </c>
       <c r="C55" t="n">
         <v>3</v>
@@ -1615,68 +1615,68 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Robina Shaheen</t>
+          <t>Iqra Bibi</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>373639</v>
+        <v>373708</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Iqra Bibi</t>
+          <t>Mahnoorr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>373708</v>
+        <v>373670</v>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mahnoorr</t>
+          <t>Gul Rukh</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>373670</v>
+        <v>373644</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gul Rukh</t>
+          <t>Hijab Zahra</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>373644</v>
+        <v>373637</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -1691,11 +1691,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Hijab Zahra</t>
+          <t>Sidra Khan</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>373637</v>
+        <v>373645</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -1710,11 +1710,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sidra Khan</t>
+          <t>Summiya Hayat 123</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>373645</v>
+        <v>51020</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1310</v>
+        <v>1275</v>
       </c>
       <c r="C3" t="n">
-        <v>1259</v>
+        <v>1224</v>
       </c>
       <c r="D3" t="n">
         <v>51</v>
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="C4" t="n">
-        <v>875</v>
+        <v>886</v>
       </c>
       <c r="D4" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1701</v>
+        <v>1720</v>
       </c>
       <c r="C5" t="n">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="D5" t="n">
-        <v>868</v>
+        <v>880</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -596,10 +596,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1310</v>
+        <v>1275</v>
       </c>
       <c r="D2" t="n">
-        <v>1259</v>
+        <v>1224</v>
       </c>
       <c r="E2" t="n">
         <v>51</v>
@@ -634,13 +634,13 @@
         <v>373648</v>
       </c>
       <c r="C4" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D4" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373646</v>
       </c>
       <c r="C5" t="n">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="D5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E5" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         <v>373642</v>
       </c>
       <c r="C6" t="n">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D6" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -767,10 +767,10 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E11" t="n">
         <v>46</v>
@@ -824,13 +824,13 @@
         <v>373716</v>
       </c>
       <c r="C14" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D14" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -843,13 +843,13 @@
         <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D15" t="n">
         <v>144</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -1140,39 +1140,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nadia bibi</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>373669</v>
+        <v>752327</v>
       </c>
       <c r="C31" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D31" t="n">
         <v>73</v>
       </c>
       <c r="E31" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Nadia bibi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>752327</v>
+        <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1275</v>
+        <v>1211</v>
       </c>
       <c r="C3" t="n">
-        <v>1224</v>
+        <v>1157</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1041</v>
+        <v>1082</v>
       </c>
       <c r="C4" t="n">
-        <v>886</v>
+        <v>917</v>
       </c>
       <c r="D4" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1720</v>
+        <v>1846</v>
       </c>
       <c r="C5" t="n">
-        <v>840</v>
+        <v>875</v>
       </c>
       <c r="D5" t="n">
-        <v>880</v>
+        <v>971</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1275</v>
+        <v>1211</v>
       </c>
       <c r="D2" t="n">
-        <v>1224</v>
+        <v>1157</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="D3" t="n">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -634,13 +634,13 @@
         <v>373648</v>
       </c>
       <c r="C4" t="n">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="D4" t="n">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373646</v>
       </c>
       <c r="C5" t="n">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="D5" t="n">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="E5" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         <v>373642</v>
       </c>
       <c r="C6" t="n">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="D6" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -691,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D7" t="n">
         <v>274</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -729,13 +729,13 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="E9" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
@@ -767,70 +767,70 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373649</v>
+        <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="D12" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373658</v>
+        <v>373649</v>
       </c>
       <c r="C13" t="n">
-        <v>274</v>
+        <v>192</v>
       </c>
       <c r="D13" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E13" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373716</v>
+        <v>373658</v>
       </c>
       <c r="C14" t="n">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="D14" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15">
@@ -843,13 +843,13 @@
         <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D15" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E15" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -900,13 +900,13 @@
         <v>373692</v>
       </c>
       <c r="C18" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D18" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E18" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
@@ -1052,89 +1052,89 @@
         <v>373710</v>
       </c>
       <c r="C26" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D26" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irum ikram</t>
+          <t>Jaweria</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>541376</v>
+        <v>163495</v>
       </c>
       <c r="C27" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D27" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Irum ikram</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>373665</v>
+        <v>541376</v>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D28" t="n">
         <v>83</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Naureen</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>884887</v>
+        <v>373665</v>
       </c>
       <c r="C29" t="n">
         <v>86</v>
       </c>
       <c r="D29" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jaweria</t>
+          <t>Naureen</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>163495</v>
+        <v>884887</v>
       </c>
       <c r="C30" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D30" t="n">
         <v>82</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1147,13 +1147,13 @@
         <v>752327</v>
       </c>
       <c r="C31" t="n">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D31" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E31" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
@@ -1166,13 +1166,13 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D32" t="n">
         <v>73</v>
       </c>
       <c r="E32" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1211</v>
+        <v>1147</v>
       </c>
       <c r="C3" t="n">
-        <v>1157</v>
+        <v>1090</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1082</v>
+        <v>1100</v>
       </c>
       <c r="C4" t="n">
-        <v>917</v>
+        <v>941</v>
       </c>
       <c r="D4" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1846</v>
+        <v>1820</v>
       </c>
       <c r="C5" t="n">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="D5" t="n">
-        <v>971</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1211</v>
+        <v>1147</v>
       </c>
       <c r="D2" t="n">
-        <v>1157</v>
+        <v>1090</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="D3" t="n">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="E3" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4">
@@ -634,13 +634,13 @@
         <v>373648</v>
       </c>
       <c r="C4" t="n">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="D4" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373646</v>
       </c>
       <c r="C5" t="n">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D5" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6">
@@ -672,10 +672,10 @@
         <v>373642</v>
       </c>
       <c r="C6" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D6" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E6" t="n">
         <v>68</v>
@@ -691,13 +691,13 @@
         <v>373696</v>
       </c>
       <c r="C7" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D7" t="n">
         <v>274</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -729,13 +729,13 @@
         <v>373651</v>
       </c>
       <c r="C9" t="n">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E9" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
@@ -767,13 +767,13 @@
         <v>373705</v>
       </c>
       <c r="C11" t="n">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -786,13 +786,13 @@
         <v>373716</v>
       </c>
       <c r="C12" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D12" t="n">
         <v>183</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -843,13 +843,13 @@
         <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D15" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -900,13 +900,13 @@
         <v>373692</v>
       </c>
       <c r="C18" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D18" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E18" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19">
@@ -1033,10 +1033,10 @@
         <v>453925</v>
       </c>
       <c r="C25" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D25" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1052,13 +1052,13 @@
         <v>373710</v>
       </c>
       <c r="C26" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D26" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E26" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -1121,39 +1121,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Naureen</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>884887</v>
+        <v>752327</v>
       </c>
       <c r="C30" t="n">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="D30" t="n">
         <v>82</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Naureen</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>752327</v>
+        <v>884887</v>
       </c>
       <c r="C31" t="n">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="D31" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E31" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1166,13 +1166,13 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D32" t="n">
         <v>73</v>
       </c>
       <c r="E32" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1147</v>
+        <v>1126</v>
       </c>
       <c r="C3" t="n">
-        <v>1090</v>
+        <v>1063</v>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1100</v>
+        <v>1120</v>
       </c>
       <c r="C4" t="n">
-        <v>941</v>
+        <v>956</v>
       </c>
       <c r="D4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1820</v>
+        <v>1839</v>
       </c>
       <c r="C5" t="n">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="D5" t="n">
-        <v>937</v>
+        <v>948</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1147</v>
+        <v>1126</v>
       </c>
       <c r="D2" t="n">
-        <v>1090</v>
+        <v>1063</v>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D3" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E3" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
@@ -634,13 +634,13 @@
         <v>373648</v>
       </c>
       <c r="C4" t="n">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D4" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
@@ -653,13 +653,13 @@
         <v>373646</v>
       </c>
       <c r="C5" t="n">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="D5" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E5" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         <v>373642</v>
       </c>
       <c r="C6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
         <v>286</v>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -703,77 +703,77 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mehran Khan</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373684</v>
+        <v>373651</v>
       </c>
       <c r="C8" t="n">
-        <v>293</v>
+        <v>416</v>
       </c>
       <c r="D8" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Mehran Khan</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373651</v>
+        <v>373684</v>
       </c>
       <c r="C9" t="n">
-        <v>407</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kainat</t>
+          <t>Mahnoor</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373712</v>
+        <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>308</v>
+        <v>258</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E10" t="n">
-        <v>101</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahnoor</t>
+          <t>Kainat</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>373705</v>
+        <v>373712</v>
       </c>
       <c r="C11" t="n">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -843,13 +843,13 @@
         <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D15" t="n">
         <v>147</v>
       </c>
       <c r="E15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -988,58 +988,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Muhammad Yousaf</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>373690</v>
+        <v>453925</v>
       </c>
       <c r="C23" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D23" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Muhammad Yousaf</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>564273</v>
+        <v>373690</v>
       </c>
       <c r="C24" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D24" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>453925</v>
+        <v>564273</v>
       </c>
       <c r="C25" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D25" t="n">
         <v>93</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1634,49 +1634,47 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mahnoorr</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>373670</v>
-      </c>
+          <t>Shafaq.zahra</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Gul Rukh</t>
+          <t>Mahnoorr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>373644</v>
+        <v>373670</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Hijab Zahra</t>
+          <t>Gul Rukh</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>373637</v>
+        <v>373644</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -1691,11 +1689,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sidra Khan</t>
+          <t>Hijab Zahra</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>373645</v>
+        <v>373637</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -1710,11 +1708,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Summiya Hayat 123</t>
+          <t>Sidra Khan</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>51020</v>
+        <v>373645</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -1723,6 +1721,25 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Summiya Hayat 123</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>51020</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="C3" t="n">
-        <v>1063</v>
+        <v>1053</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1120</v>
+        <v>1134</v>
       </c>
       <c r="C4" t="n">
-        <v>956</v>
+        <v>970</v>
       </c>
       <c r="D4" t="n">
         <v>164</v>
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1839</v>
+        <v>1859</v>
       </c>
       <c r="C5" t="n">
-        <v>891</v>
+        <v>901</v>
       </c>
       <c r="D5" t="n">
-        <v>948</v>
+        <v>958</v>
       </c>
     </row>
     <row r="6">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>67</v>
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="D2" t="n">
-        <v>1063</v>
+        <v>1053</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -615,51 +615,51 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="D3" t="n">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="E3" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373648</v>
+        <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="D4" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373646</v>
+        <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>491</v>
+        <v>444</v>
       </c>
       <c r="D5" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E5" t="n">
-        <v>130</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -748,13 +748,13 @@
         <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D10" t="n">
         <v>208</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -843,10 +843,10 @@
         <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D15" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E15" t="n">
         <v>35</v>
@@ -969,39 +969,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>373699</v>
+        <v>453925</v>
       </c>
       <c r="C22" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" t="n">
         <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>453925</v>
+        <v>373699</v>
       </c>
       <c r="C23" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D23" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1052,10 +1052,10 @@
         <v>373710</v>
       </c>
       <c r="C26" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D26" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
@@ -1083,58 +1083,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Irum ikram</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>541376</v>
+        <v>752327</v>
       </c>
       <c r="C28" t="n">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="D28" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Irum ikram</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>373665</v>
+        <v>541376</v>
       </c>
       <c r="C29" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D29" t="n">
         <v>83</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>752327</v>
+        <v>373665</v>
       </c>
       <c r="C30" t="n">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="D30" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E30" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1121</v>
+        <v>1107</v>
       </c>
       <c r="C3" t="n">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1134</v>
+        <v>1154</v>
       </c>
       <c r="C4" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="D4" t="n">
         <v>164</v>
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1859</v>
+        <v>1878</v>
       </c>
       <c r="C5" t="n">
-        <v>901</v>
+        <v>910</v>
       </c>
       <c r="D5" t="n">
-        <v>958</v>
+        <v>968</v>
       </c>
     </row>
     <row r="6">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>67</v>
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1121</v>
+        <v>1107</v>
       </c>
       <c r="D2" t="n">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -615,51 +615,51 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="D3" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373646</v>
+        <v>373648</v>
       </c>
       <c r="C4" t="n">
-        <v>497</v>
+        <v>448</v>
       </c>
       <c r="D4" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E4" t="n">
-        <v>132</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373648</v>
+        <v>373646</v>
       </c>
       <c r="C5" t="n">
-        <v>444</v>
+        <v>499</v>
       </c>
       <c r="D5" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         <v>373642</v>
       </c>
       <c r="C6" t="n">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D6" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -748,10 +748,10 @@
         <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E10" t="n">
         <v>51</v>
@@ -843,13 +843,13 @@
         <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D15" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -976,10 +976,10 @@
         <v>453925</v>
       </c>
       <c r="C22" t="n">
+        <v>104</v>
+      </c>
+      <c r="D22" t="n">
         <v>102</v>
-      </c>
-      <c r="D22" t="n">
-        <v>100</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -1007,96 +1007,96 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Muhammad Yousaf</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>373690</v>
+        <v>373710</v>
       </c>
       <c r="C24" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D24" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Muhammad Yousaf</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>564273</v>
+        <v>373690</v>
       </c>
       <c r="C25" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D25" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>373710</v>
+        <v>564273</v>
       </c>
       <c r="C26" t="n">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="D26" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jaweria</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>163495</v>
+        <v>752327</v>
       </c>
       <c r="C27" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="D27" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Jaweria</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>752327</v>
+        <v>163495</v>
       </c>
       <c r="C28" t="n">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="D28" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E28" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">

--- a/Error_log/Weekly_QA_Summary.xlsx
+++ b/Error_log/Weekly_QA_Summary.xlsx
@@ -470,33 +470,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tracking vs Household</t>
+          <t>Girls</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1107</v>
+        <v>1266</v>
       </c>
       <c r="C3" t="n">
-        <v>1038</v>
+        <v>1102</v>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Girls</t>
+          <t>Tracking vs Household</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1154</v>
+        <v>1096</v>
       </c>
       <c r="C4" t="n">
-        <v>990</v>
+        <v>1025</v>
       </c>
       <c r="D4" t="n">
-        <v>164</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1878</v>
+        <v>1915</v>
       </c>
       <c r="C5" t="n">
-        <v>910</v>
+        <v>932</v>
       </c>
       <c r="D5" t="n">
-        <v>968</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -596,13 +596,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1107</v>
+        <v>1096</v>
       </c>
       <c r="D2" t="n">
-        <v>1038</v>
+        <v>1025</v>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -615,51 +615,51 @@
         <v>373641</v>
       </c>
       <c r="C3" t="n">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="D3" t="n">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="E3" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shazia Bibi</t>
+          <t>Shafaq Zahra</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373648</v>
+        <v>373646</v>
       </c>
       <c r="C4" t="n">
-        <v>448</v>
+        <v>519</v>
       </c>
       <c r="D4" t="n">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shafaq Zahra</t>
+          <t>Shazia Bibi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>373646</v>
+        <v>373648</v>
       </c>
       <c r="C5" t="n">
-        <v>499</v>
+        <v>452</v>
       </c>
       <c r="D5" t="n">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
@@ -672,51 +672,51 @@
         <v>373642</v>
       </c>
       <c r="C6" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D6" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shazia begum</t>
+          <t>Javairia</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>373696</v>
+        <v>373651</v>
       </c>
       <c r="C7" t="n">
-        <v>317</v>
+        <v>429</v>
       </c>
       <c r="D7" t="n">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Javairia</t>
+          <t>Shazia begum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>373651</v>
+        <v>373696</v>
       </c>
       <c r="C8" t="n">
-        <v>416</v>
+        <v>324</v>
       </c>
       <c r="D8" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="E8" t="n">
-        <v>148</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -748,10 +748,10 @@
         <v>373705</v>
       </c>
       <c r="C10" t="n">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="E10" t="n">
         <v>51</v>
@@ -767,10 +767,10 @@
         <v>373712</v>
       </c>
       <c r="C11" t="n">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="E11" t="n">
         <v>101</v>
@@ -779,58 +779,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Naureen Khan</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>373716</v>
+        <v>373658</v>
       </c>
       <c r="C12" t="n">
-        <v>214</v>
+        <v>281</v>
       </c>
       <c r="D12" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sadia Rustum</t>
+          <t>Naureen Khan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>373649</v>
+        <v>373716</v>
       </c>
       <c r="C13" t="n">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="D13" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Sadia Rustum</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>373658</v>
+        <v>373649</v>
       </c>
       <c r="C14" t="n">
-        <v>274</v>
+        <v>192</v>
       </c>
       <c r="D14" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E14" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -843,51 +843,51 @@
         <v>373706</v>
       </c>
       <c r="C15" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D15" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Khalida Bibi</t>
+          <t>Rehana Bibi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>373673</v>
+        <v>373691</v>
       </c>
       <c r="C16" t="n">
-        <v>140</v>
+        <v>275</v>
       </c>
       <c r="D16" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rehana Bibi</t>
+          <t>Khalida Bibi</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373691</v>
+        <v>373673</v>
       </c>
       <c r="C17" t="n">
-        <v>265</v>
+        <v>140</v>
       </c>
       <c r="D17" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E17" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -900,10 +900,10 @@
         <v>373692</v>
       </c>
       <c r="C18" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D18" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E18" t="n">
         <v>131</v>
@@ -950,134 +950,134 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Asma Gull</t>
+          <t>Naureen khan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>373672</v>
+        <v>453925</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D21" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Naureen khan</t>
+          <t>Summiya Hayat</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>453925</v>
+        <v>373710</v>
       </c>
       <c r="C22" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ishaq Khan</t>
+          <t>Asma Gull</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>373699</v>
+        <v>373672</v>
       </c>
       <c r="C23" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Summiya Hayat</t>
+          <t>Ishaq Khan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>373710</v>
+        <v>373699</v>
       </c>
       <c r="C24" t="n">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="D24" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E24" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Muhammad Yousaf</t>
+          <t>aisha.aman</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>373690</v>
+        <v>752327</v>
       </c>
       <c r="C25" t="n">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="D25" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lati Khan</t>
+          <t>Muhammad Yousaf</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>564273</v>
+        <v>373690</v>
       </c>
       <c r="C26" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D26" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>aisha.aman</t>
+          <t>Lati Khan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>752327</v>
+        <v>564273</v>
       </c>
       <c r="C27" t="n">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="D27" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E27" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1166,10 +1166,10 @@
         <v>373669</v>
       </c>
       <c r="C32" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D32" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E32" t="n">
         <v>35</v>
